--- a/Listado de Tiendas_Augusto.xlsx
+++ b/Listado de Tiendas_Augusto.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\desarrollo\Euro\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Desarrollos\u_\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA9C50FA-0FFD-4881-8F83-81B5579428FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1923D4D-F160-47EE-A206-668458435CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{4944A775-6BF1-43BB-880A-09CB389DE030}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{4944A775-6BF1-43BB-880A-09CB389DE030}"/>
   </bookViews>
   <sheets>
     <sheet name="CHEDRAUI" sheetId="1" r:id="rId1"/>
     <sheet name="LA COMER" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CHEDRAUI!$A$2:$F$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CHEDRAUI!$A$1:$I$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'LA COMER'!$A$2:$F$50</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="583">
   <si>
     <t>Tienda</t>
   </si>
@@ -676,273 +676,18 @@
     <t>https://maps.app.goo.gl/YqEtAY5gpfYk1G8b8</t>
   </si>
   <si>
-    <t>-87.06798558561513</t>
-  </si>
-  <si>
-    <t>-99.16256245868308</t>
-  </si>
-  <si>
-    <t>-99.09476002169852</t>
-  </si>
-  <si>
-    <t>-99.13325619178252</t>
-  </si>
-  <si>
-    <t>-99.27452080000008</t>
-  </si>
-  <si>
-    <t>-99.20632122454965</t>
-  </si>
-  <si>
-    <t>-89.63013942886305</t>
-  </si>
-  <si>
-    <t>-96.12896520000012</t>
-  </si>
-  <si>
-    <t>-96.11878897750798</t>
-  </si>
-  <si>
-    <t>-96.70897963247428</t>
-  </si>
-  <si>
-    <t>110.33133376166542</t>
-  </si>
-  <si>
-    <t>-99.11860706186492</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -86.8653475633218</t>
-  </si>
-  <si>
-    <t>-100.3601296042713</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -99.1982812146724</t>
-  </si>
-  <si>
-    <t>100.44857560463508</t>
-  </si>
-  <si>
-    <t>103.39910819143172</t>
-  </si>
-  <si>
-    <t>-89.57855710936339</t>
-  </si>
-  <si>
-    <t>-96.88430677416497</t>
-  </si>
-  <si>
-    <t>100.79619298192713</t>
-  </si>
-  <si>
-    <t>-98.26696156968366</t>
-  </si>
-  <si>
-    <t>21.153669625826232</t>
-  </si>
-  <si>
-    <t>-86.84084126951414</t>
-  </si>
-  <si>
-    <t>-99.77421559833182</t>
-  </si>
-  <si>
-    <t>19.674092001861467</t>
-  </si>
-  <si>
-    <t>101.16174896828636</t>
-  </si>
-  <si>
-    <t>-99.62838266934415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6491413565163, </t>
-  </si>
-  <si>
-    <t>20.72275971315653,</t>
-  </si>
-  <si>
-    <t>18.97016877309698,</t>
-  </si>
-  <si>
-    <t>20.211670549295192</t>
-  </si>
-  <si>
-    <t>21.00560773518514,</t>
-  </si>
-  <si>
-    <t>19.394017884968605</t>
-  </si>
-  <si>
-    <t>16.75350652352252,</t>
-  </si>
-  <si>
-    <t>17.966141746100455</t>
-  </si>
-  <si>
-    <t>20.670603619910793</t>
-  </si>
-  <si>
-    <t>22.155287945724343</t>
-  </si>
-  <si>
-    <t>19.433307411070828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0740956004798, </t>
-  </si>
-  <si>
-    <t>19.154562842751485</t>
-  </si>
-  <si>
-    <t>21.146932163015293</t>
-  </si>
-  <si>
-    <t>19.524946937011883</t>
-  </si>
-  <si>
-    <t>20.502512202245953</t>
-  </si>
-  <si>
-    <t>20.50918099622088,</t>
-  </si>
-  <si>
     <t>19.310666760356014</t>
   </si>
   <si>
-    <t>21.13585756039021,</t>
-  </si>
-  <si>
     <t>24.165825561511703</t>
   </si>
   <si>
-    <t>20.68269893678712,</t>
-  </si>
-  <si>
-    <t>15.86273577769884,</t>
-  </si>
-  <si>
-    <t>19.09316308310847,</t>
-  </si>
-  <si>
-    <t>19.412199279269327</t>
-  </si>
-  <si>
-    <t>23.044193402640495</t>
-  </si>
-  <si>
-    <t>20.846691995269833</t>
-  </si>
-  <si>
-    <t>19.407302494929457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5466871715793, </t>
-  </si>
-  <si>
-    <t>19.299447556554625</t>
-  </si>
-  <si>
-    <t>21.523571408612572</t>
-  </si>
-  <si>
-    <t>19.571521571878584</t>
-  </si>
-  <si>
-    <t>-87.08338616424722</t>
-  </si>
-  <si>
-    <t>103.41543166920151</t>
-  </si>
-  <si>
-    <t>-98.28524509741118</t>
-  </si>
-  <si>
-    <t>-87.45016642702112</t>
-  </si>
-  <si>
-    <t>-89.69030698174097</t>
-  </si>
-  <si>
-    <t>, -99.172988697729</t>
-  </si>
-  <si>
-    <t>-93.14991221400547</t>
-  </si>
-  <si>
-    <t>-92.94039642708981</t>
-  </si>
-  <si>
-    <t>-87.06026906938096</t>
-  </si>
-  <si>
-    <t>101.00362542406998</t>
-  </si>
-  <si>
-    <t>-99.18374815846853</t>
-  </si>
-  <si>
-    <t>-98.25756335332647</t>
-  </si>
-  <si>
-    <t>-96.10000743947634</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -86.8226724264085</t>
-  </si>
-  <si>
-    <t>-99.22968672599114</t>
-  </si>
-  <si>
-    <t>-86.95793916922445</t>
-  </si>
-  <si>
-    <t>-87.22534771145233</t>
-  </si>
-  <si>
     <t>-99.63525232219332</t>
   </si>
   <si>
-    <t>-86.74816566769019</t>
-  </si>
-  <si>
     <t>110.31221644427187</t>
   </si>
   <si>
-    <t>103.43395034009926</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -97.0673412982811</t>
-  </si>
-  <si>
-    <t>-96.10348361331118</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -99.1647493201847</t>
-  </si>
-  <si>
-    <t>109.70713986526968</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -86.8772162304825</t>
-  </si>
-  <si>
-    <t>-99.16782701562761</t>
-  </si>
-  <si>
-    <t>100.39714204067191</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -99.2126284394842</t>
-  </si>
-  <si>
-    <t>-87.37931112469501</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -99.3007761760591</t>
-  </si>
-  <si>
     <t xml:space="preserve">Latitud </t>
   </si>
   <si>
@@ -1198,10 +943,853 @@
     <t>Long</t>
   </si>
   <si>
-    <t xml:space="preserve">18.010234580182164, </t>
-  </si>
-  <si>
-    <t>-92.9790302711646</t>
+    <t>Cadena</t>
+  </si>
+  <si>
+    <t>Chedraui</t>
+  </si>
+  <si>
+    <t>La Comer</t>
+  </si>
+  <si>
+    <t>21.926540498877767</t>
+  </si>
+  <si>
+    <t>-102.29543018712641</t>
+  </si>
+  <si>
+    <t>Corregido</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/NPkZnk1S5TVgy25w5</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/7Kci2QcWqrVwFA2q8</t>
+  </si>
+  <si>
+    <t>24.14338081409374</t>
+  </si>
+  <si>
+    <t>-110.33135186010179</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/su2deXo1YV24sjUm7</t>
+  </si>
+  <si>
+    <t>-110.31214808694857</t>
+  </si>
+  <si>
+    <t>24.164367279723486</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/2SiPauafuFV5RLuC9</t>
+  </si>
+  <si>
+    <t>-109.7072351500626</t>
+  </si>
+  <si>
+    <t>23.043941712256192</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/tZnk6bs8et2Cp2bC8</t>
+  </si>
+  <si>
+    <t>-109.90900318774915</t>
+  </si>
+  <si>
+    <t>22.888679646932005</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/VferGyTxkcmF6ybn7</t>
+  </si>
+  <si>
+    <t>-110.30758312882568</t>
+  </si>
+  <si>
+    <t>24.152324650691337</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/BhQjBQ79digNYf2F6</t>
+  </si>
+  <si>
+    <t>-110.3115936178058</t>
+  </si>
+  <si>
+    <t>24.139497338415417</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/sRMWgJ7vT6C2Toeg7</t>
+  </si>
+  <si>
+    <t>-110.30240260390913</t>
+  </si>
+  <si>
+    <t>24.14917478763409</t>
+  </si>
+  <si>
+    <t>Municipio</t>
+  </si>
+  <si>
+    <t>Localidad</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/X7KJ6j4bDDWxiaie6</t>
+  </si>
+  <si>
+    <t>-93.14985669513878</t>
+  </si>
+  <si>
+    <t>16.75340396106373</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/GrbZ9RwiLx4yRMPF9</t>
+  </si>
+  <si>
+    <t>-99.1625244441631</t>
+  </si>
+  <si>
+    <t>19.37366803010571</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/8shmhmjYSyfodYt48</t>
+  </si>
+  <si>
+    <t>-99.09474706440932</t>
+  </si>
+  <si>
+    <t>19.43978742768164</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/4yKhL4AxRM8rTboXA</t>
+  </si>
+  <si>
+    <t>Gustavo A. Madero</t>
+  </si>
+  <si>
+    <t>Venustiano Carranza</t>
+  </si>
+  <si>
+    <t>Benito Juárez</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/vECm4aJUL1K265XCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.483559691002196 </t>
+  </si>
+  <si>
+    <t>-99.13324845057397</t>
+  </si>
+  <si>
+    <t>-99.27471411926209</t>
+  </si>
+  <si>
+    <t>19.36035664194075</t>
+  </si>
+  <si>
+    <t>Cuajimalpa de Morelos</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/LExvaGRPetnf5LBp7</t>
+  </si>
+  <si>
+    <t>Miguel Hidalgo</t>
+  </si>
+  <si>
+    <t>-99.206290670684</t>
+  </si>
+  <si>
+    <t>19.440621852151473</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/p5setDHPCLhqpEfg8</t>
+  </si>
+  <si>
+    <t>Coayoacán</t>
+  </si>
+  <si>
+    <t>-99.11852521800147</t>
+  </si>
+  <si>
+    <t>19.30430387736326</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/E8YiMxaamDFfx8qVA</t>
+  </si>
+  <si>
+    <t>-99.19833224307936</t>
+  </si>
+  <si>
+    <t>19.334868008225314</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/m11ZUBQaDCxSgnpz8</t>
+  </si>
+  <si>
+    <t>-99.17299264315815</t>
+  </si>
+  <si>
+    <t>19.393914787090132</t>
+  </si>
+  <si>
+    <t>Bien</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/gQTRzH7C5hCVaEj19</t>
+  </si>
+  <si>
+    <t>19.433448209930205</t>
+  </si>
+  <si>
+    <t>-99.18389685893533</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/BtYCzpMoo1kvR26L7</t>
+  </si>
+  <si>
+    <t>Cuauhtémoc</t>
+  </si>
+  <si>
+    <t>-99.1646914774591</t>
+  </si>
+  <si>
+    <t>19.412168102714727</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/FnjziPaimr4nHaSD8</t>
+  </si>
+  <si>
+    <t>-99.16786966858302</t>
+  </si>
+  <si>
+    <t>19.407343403514012</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/bVYaYmS9fjnZzhYZA</t>
+  </si>
+  <si>
+    <t>Tlapan</t>
+  </si>
+  <si>
+    <t>-99.21272500436206</t>
+  </si>
+  <si>
+    <t>19.299457700458227</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/DKHxQFF5vkY32gmT6</t>
+  </si>
+  <si>
+    <t>Álvaro Obregón</t>
+  </si>
+  <si>
+    <t>-99.2582684711642</t>
+  </si>
+  <si>
+    <t>19.36876390277518</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/27vfk9qAbERqQBwN9</t>
+  </si>
+  <si>
+    <t>-99.18808930817768</t>
+  </si>
+  <si>
+    <t>19.3472209855802</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/odk19uwXb6nAipFn7</t>
+  </si>
+  <si>
+    <t>-99.23267699128822</t>
+  </si>
+  <si>
+    <t>19.42264156702739</t>
+  </si>
+  <si>
+    <t>Naucalpan de Juárez</t>
+  </si>
+  <si>
+    <t>Tecamachalco</t>
+  </si>
+  <si>
+    <t>Metepec</t>
+  </si>
+  <si>
+    <t>Huatulco</t>
+  </si>
+  <si>
+    <t>Juriquilla</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/5FBBCumqy6b7ZvA97</t>
+  </si>
+  <si>
+    <t>19.428188327615796</t>
+  </si>
+  <si>
+    <t>-99.21047103134539</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/kpf6UGFQbFtoARVN9</t>
+  </si>
+  <si>
+    <t>-99.219002787166</t>
+  </si>
+  <si>
+    <t>19.454292307948833</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/zyRvmjYjBfMGkwhG8</t>
+  </si>
+  <si>
+    <t>-99.62827538531845</t>
+  </si>
+  <si>
+    <t>19.258725023277446</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/ro3g2SMjndVzJxjg8</t>
+  </si>
+  <si>
+    <t>-99.22964381600076</t>
+  </si>
+  <si>
+    <t>19.524967272003394</t>
+  </si>
+  <si>
+    <t>Tlalnepantla</t>
+  </si>
+  <si>
+    <t>Lerma de Villada</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Ny3i8gmEBHeto83X6</t>
+  </si>
+  <si>
+    <t>99.50441303253459</t>
+  </si>
+  <si>
+    <t>19.28500860011968</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/NwYGR9gdo2R8yvKTA</t>
+  </si>
+  <si>
+    <t>-99.30084123273592</t>
+  </si>
+  <si>
+    <t>19.57133829013913</t>
+  </si>
+  <si>
+    <t>Atizapán de Zaragoza</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/TSnk7BeC9MReTWiTA</t>
+  </si>
+  <si>
+    <t>-99.21278042949338</t>
+  </si>
+  <si>
+    <t>19.52404937292314</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/WRuA8qxyUwGkc7HC9</t>
+  </si>
+  <si>
+    <t>-99.23109190065897</t>
+  </si>
+  <si>
+    <t>19.436449317339328</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/T1K9tQBVpdCekfDn9</t>
+  </si>
+  <si>
+    <t>-99.28128751600266</t>
+  </si>
+  <si>
+    <t>19.40443356431078</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/KKpzpVc2Lg5ssWdw6</t>
+  </si>
+  <si>
+    <t>19.393217765125012</t>
+  </si>
+  <si>
+    <t>-99.28199883134585</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Kd9i9QUsNpUU2gsS6</t>
+  </si>
+  <si>
+    <t>Celaya</t>
+  </si>
+  <si>
+    <t>Morelia</t>
+  </si>
+  <si>
+    <t>Tulum</t>
+  </si>
+  <si>
+    <t>Cozumel</t>
+  </si>
+  <si>
+    <t>20.518979981484232</t>
+  </si>
+  <si>
+    <t>-100.79625734112005</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/yVpDunhRGYpNJ9i97</t>
+  </si>
+  <si>
+    <t>Acapulco de Juárez</t>
+  </si>
+  <si>
+    <t>Oaxaca de Juárez</t>
+  </si>
+  <si>
+    <t>16.771416359633207</t>
+  </si>
+  <si>
+    <t>-99.77422496385825</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/KDWtDXU62NeFuusu9</t>
+  </si>
+  <si>
+    <t>Pachuca de Soto</t>
+  </si>
+  <si>
+    <t>20.037041155183136</t>
+  </si>
+  <si>
+    <t>-98.79685243133603</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/81ZsvQ7NKB6V3nCK7</t>
+  </si>
+  <si>
+    <t>Villahermosa</t>
+  </si>
+  <si>
+    <t>Xalapa</t>
+  </si>
+  <si>
+    <t>20.679371308029193</t>
+  </si>
+  <si>
+    <t>-103.39969698529637</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/QrmraqZQ777Gsztw8</t>
+  </si>
+  <si>
+    <t>-103.4155067755042</t>
+  </si>
+  <si>
+    <t>20.722940357064253</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/tJz9yhnTULhApZUPA</t>
+  </si>
+  <si>
+    <t>Zapopan</t>
+  </si>
+  <si>
+    <t>-103.43402544666904</t>
+  </si>
+  <si>
+    <t>20.682678979874527</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/NvRHh3HYKn8YafA97</t>
+  </si>
+  <si>
+    <t>Chetumal</t>
+  </si>
+  <si>
+    <t>-101.16180261784903</t>
+  </si>
+  <si>
+    <t>19.674243652123394</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/YT2h2ASdi2VMgHLBA</t>
+  </si>
+  <si>
+    <t>Holbox</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/kZTNd55ydv9UnMfU8</t>
+  </si>
+  <si>
+    <t>-96.12899736591714</t>
+  </si>
+  <si>
+    <t>15.762813656793565</t>
+  </si>
+  <si>
+    <t>-96.70904131224518</t>
+  </si>
+  <si>
+    <t>17.078464203817184</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/kTCX3fknvrvXaKLa6</t>
+  </si>
+  <si>
+    <t>Puerto Escondido</t>
+  </si>
+  <si>
+    <t>Puerto Aventuras</t>
+  </si>
+  <si>
+    <t>-97.06735203139438</t>
+  </si>
+  <si>
+    <t>15.862720312113414</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/e1KxmU9DV3dDsAhp7</t>
+  </si>
+  <si>
+    <t>-98.26693577089603</t>
+  </si>
+  <si>
+    <t>19.005884969268667</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/mworPRYu4Do8DY5X6</t>
+  </si>
+  <si>
+    <t>-98.28530947553121</t>
+  </si>
+  <si>
+    <t>18.97020946648421</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/1p9pAtMVibFYVLSx5</t>
+  </si>
+  <si>
+    <t>Puebla de Zaragoza</t>
+  </si>
+  <si>
+    <t>-98.257574101368</t>
+  </si>
+  <si>
+    <t>19.074075293164082</t>
+  </si>
+  <si>
+    <t>Santiago de Querétaro</t>
+  </si>
+  <si>
+    <t>20.57240848572954</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/aM5e7JWTYu6QwQEo8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/9V9yVtqhW45EXsMDA</t>
+  </si>
+  <si>
+    <t>-100.44866144666895</t>
+  </si>
+  <si>
+    <t>20.691018859448537</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/uFwaYPm8QxGpVUhVA</t>
+  </si>
+  <si>
+    <t>Playa del Carmen</t>
+  </si>
+  <si>
+    <t>-87.06797013132656</t>
+  </si>
+  <si>
+    <t>20.63515486709839</t>
+  </si>
+  <si>
+    <t>Pendiente</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/EbEbNQt6sXEGGHhdA</t>
+  </si>
+  <si>
+    <t>Cancún</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/n74AGDN6kscamFFC6</t>
+  </si>
+  <si>
+    <t>20.625364969629413</t>
+  </si>
+  <si>
+    <t>-87.08472095195519</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/3PSX5wV7THR2Ms6f8</t>
+  </si>
+  <si>
+    <t>-86.84089491782565</t>
+  </si>
+  <si>
+    <t>21.153709668808098</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/uaPihkobVSSgqW2b6</t>
+  </si>
+  <si>
+    <t>-87.08341991766505</t>
+  </si>
+  <si>
+    <t>20.649256270532153</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/q2zPSgaBeQUcZwhf7</t>
+  </si>
+  <si>
+    <t>-87.45011278715432</t>
+  </si>
+  <si>
+    <t>20.211620226750274</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/aUsf9WLtyXcxycnu6</t>
+  </si>
+  <si>
+    <t>-87.06020470063974</t>
+  </si>
+  <si>
+    <t>20.67067390614974</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/3t6iBexLjzPxaYab6</t>
+  </si>
+  <si>
+    <t>21.146902163012815</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Du8jwj5yLy7CSveW6</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -86.95804646201502</t>
+  </si>
+  <si>
+    <t>20.502552418105005</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/c3TLSQV3DURppDwv8</t>
+  </si>
+  <si>
+    <t>-87.22544427550761</t>
+  </si>
+  <si>
+    <t>20.50918101546872</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/M78TQsmYqSEDR34G6</t>
+  </si>
+  <si>
+    <t>-86.74808954475661</t>
+  </si>
+  <si>
+    <t>21.13582878997776</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/6pTyy2tbKrDVk7PC6</t>
+  </si>
+  <si>
+    <t>Puerto Morelos</t>
+  </si>
+  <si>
+    <t>-86.87703331982648</t>
+  </si>
+  <si>
+    <t>20.847263664278568</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/6yey8pxeFJcX5Xh89</t>
+  </si>
+  <si>
+    <t>Manzanillo</t>
+  </si>
+  <si>
+    <t>-87.37923602761104</t>
+  </si>
+  <si>
+    <t>21.52369119723223</t>
+  </si>
+  <si>
+    <t>Lázaro Cárdenas</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/eP34swJnwY7xwYAu6</t>
+  </si>
+  <si>
+    <t>-86.89844807484765</t>
+  </si>
+  <si>
+    <t>20.85717008166764</t>
+  </si>
+  <si>
+    <t>-88.32042498717979</t>
+  </si>
+  <si>
+    <t>18.520357934206164</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/ysaT9Qdea4ptCtFP9</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/vkusanre8bEFt74J8</t>
+  </si>
+  <si>
+    <t>-101.00368980246573</t>
+  </si>
+  <si>
+    <t>22.155347586695733</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/TdBcGY7nt3XZrRW38</t>
+  </si>
+  <si>
+    <t>-92.9433859197241</t>
+  </si>
+  <si>
+    <t>17.995308875170785</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/RXnwXkirPjogcS5r5</t>
+  </si>
+  <si>
+    <t>-92.9790410004356</t>
+  </si>
+  <si>
+    <t>18.01132121090834</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/FsxfSeba1pPxi6jj9</t>
+  </si>
+  <si>
+    <t>-92.9404071602025</t>
+  </si>
+  <si>
+    <t>17.96612135131965</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/5UnD1Qzyu4sxRu859</t>
+  </si>
+  <si>
+    <t>-96.11885339087151</t>
+  </si>
+  <si>
+    <t>19.16072905788178</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/vr593zPNFHAcb2wcA</t>
+  </si>
+  <si>
+    <t>19.521051215238074</t>
+  </si>
+  <si>
+    <t>-96.88444837552294</t>
+  </si>
+  <si>
+    <t>Xalapa-Enríquez</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/cTgiU6dDUYWAyvTU9</t>
+  </si>
+  <si>
+    <t>Boca del Río</t>
+  </si>
+  <si>
+    <t>-96.0999859871705</t>
+  </si>
+  <si>
+    <t>19.154446309667456</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/jiLUjfPFZUtqA9Mo9</t>
+  </si>
+  <si>
+    <t>-96.10346216018615</t>
+  </si>
+  <si>
+    <t>19.093244209069347</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/soVVL5N1ZKChufXv7</t>
+  </si>
+  <si>
+    <t>-96.8568329583294</t>
+  </si>
+  <si>
+    <t>19.507011350939308</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/8hLgmeL7GeGef3oTA</t>
+  </si>
+  <si>
+    <t>-89.5967516091437</t>
+  </si>
+  <si>
+    <t>21.020911581122405</t>
+  </si>
+  <si>
+    <t>Mérida</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Vb4GkKYM5zzLUSaE9</t>
+  </si>
+  <si>
+    <t>-89.63000308529074</t>
+  </si>
+  <si>
+    <t>21.03018053690969</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/p1Cxn1WTYUYnxsPG7</t>
+  </si>
+  <si>
+    <t>-89.57912621597721</t>
+  </si>
+  <si>
+    <t>21.020797332916803</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/nj5ddiJMqxfWhotY6</t>
+  </si>
+  <si>
+    <t>-89.69042500433538</t>
+  </si>
+  <si>
+    <t>21.005687981898078</t>
+  </si>
+  <si>
+    <t>-99.27471683359842</t>
+  </si>
+  <si>
+    <t>19.39942108841918</t>
+  </si>
+  <si>
+    <t>Avandaro</t>
+  </si>
+  <si>
+    <t>San José del Cabo</t>
+  </si>
+  <si>
+    <t>San Miguel de Allende</t>
+  </si>
+  <si>
+    <t>Cabo San Lucas</t>
+  </si>
+  <si>
+    <t>Valle de Bravo</t>
   </si>
 </sst>
 </file>
@@ -1211,7 +1799,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1253,8 +1841,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1285,8 +1880,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1334,12 +1941,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.79998168889431442"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1391,6 +2007,43 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1410,9 +2063,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1450,7 +2103,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1556,7 +2209,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1698,7 +2351,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1706,2091 +2359,4408 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D5E50-5E35-4FAD-9B00-6AD6C3942E5B}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A2:J80"/>
+  <dimension ref="A1:N1048576"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="66" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" customWidth="1"/>
-    <col min="7" max="7" width="27.140625" customWidth="1"/>
-    <col min="8" max="8" width="35.28515625" customWidth="1"/>
-    <col min="9" max="9" width="19.85546875" style="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" hidden="1" customWidth="1"/>
+    <col min="7" max="8" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" customWidth="1"/>
+    <col min="10" max="10" width="44.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.28515625" customWidth="1"/>
+    <col min="12" max="12" width="19.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21" style="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="1" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G1" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="J1" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="L1" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="M1" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="N1" s="16"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>196</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2" s="7">
+        <v>1.3838290082880884E-2</v>
+      </c>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="6">
+        <v>10</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>306</v>
+      </c>
+      <c r="K2" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="L2" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="M2" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N2" s="16"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>127</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" s="7">
+        <v>2.159342568746472E-2</v>
+      </c>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="6">
+        <v>10</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="K3" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="L3" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="M3" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N3" s="16"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>333</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="F4" s="10">
+        <v>7.8252122337391823E-3</v>
+      </c>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="6">
+        <v>5</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>310</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>312</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="M4" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N4" s="16"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>178</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="F5" s="10">
+        <v>6.0846674247843667E-3</v>
+      </c>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="6">
+        <v>10</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="K5" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="M5" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N5" s="16"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>802</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="F6" s="10">
+        <v>5.0952928104922666E-3</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="6">
+        <v>10</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>316</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="M6" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N6" s="16"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>126</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F7" s="10">
+        <v>4.2220204530022372E-3</v>
+      </c>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="6">
+        <v>10</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="L7" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N7" s="16"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>330</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="F8" s="10">
+        <v>3.7043088476581844E-3</v>
+      </c>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="6">
+        <v>7</v>
+      </c>
+      <c r="J8" s="21" t="s">
+        <v>322</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="L8" s="17" t="s">
+        <v>323</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N8" s="16"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>334</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="F9" s="10">
+        <v>1.8709650274066469E-3</v>
+      </c>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="6">
+        <v>7</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="K9" s="17" t="s">
+        <v>327</v>
+      </c>
+      <c r="L9" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N9" s="16"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>13</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="F10" s="7">
+        <v>1.12892803485364E-2</v>
+      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="6">
+        <v>10</v>
+      </c>
+      <c r="J10" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="L10" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N10" s="16"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>235</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F11" s="7">
+        <v>3.5985967166643498E-2</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="I11" s="6">
+        <v>10</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>333</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="L11" s="17" t="s">
+        <v>334</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N11" s="16"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>182</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F12" s="7">
+        <v>3.5644074373929843E-2</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="I12" s="6">
+        <v>10</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>336</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="L12" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N12" s="16"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>174</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F13" s="7">
+        <v>3.0428341835977236E-2</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="I13" s="6">
+        <v>10</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>339</v>
+      </c>
+      <c r="K13" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="L13" s="17" t="s">
+        <v>345</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N13" s="16"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>98</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" s="7">
+        <v>2.8799763282912907E-2</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="I14" s="6">
+        <v>10</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>347</v>
+      </c>
+      <c r="L14" s="17" t="s">
+        <v>346</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N14" s="16"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>232</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F15" s="7">
+        <v>2.8733897314624928E-2</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="I15" s="6">
+        <v>10</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>349</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="L15" s="17" t="s">
+        <v>351</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N15" s="16"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>233</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" s="7">
+        <v>2.1515404807174253E-2</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="I16" s="6">
+        <v>10</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="K16" s="23" t="s">
+        <v>356</v>
+      </c>
+      <c r="L16" s="23" t="s">
+        <v>355</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N16" s="16"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>177</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F17" s="7">
+        <v>2.0063778202674572E-2</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="I17" s="6">
+        <v>10</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>357</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="L17" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="N17" s="16"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>814</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F18" s="7">
+        <v>1.1317007292279867E-2</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="I18" s="6">
+        <v>8</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>360</v>
+      </c>
+      <c r="K18" s="17" t="s">
+        <v>362</v>
+      </c>
+      <c r="L18" s="17" t="s">
+        <v>361</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N18" s="16"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>587</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F19" s="10">
+        <v>9.8573962791872784E-3</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="I19" s="6">
+        <v>5</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>364</v>
+      </c>
+      <c r="K19" s="17" t="s">
+        <v>365</v>
+      </c>
+      <c r="L19" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N19" s="16"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>819</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F20" s="10">
+        <v>6.4709636133180506E-3</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="I20" s="6">
+        <v>5</v>
+      </c>
+      <c r="J20" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="K20" s="17" t="s">
+        <v>370</v>
+      </c>
+      <c r="L20" s="17" t="s">
+        <v>369</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N20" s="16"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>890</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" s="10">
+        <v>5.9978222327954078E-3</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="I21" s="6">
+        <v>4</v>
+      </c>
+      <c r="J21" s="21" t="s">
+        <v>371</v>
+      </c>
+      <c r="K21" s="17" t="s">
+        <v>373</v>
+      </c>
+      <c r="L21" s="17" t="s">
+        <v>372</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N21" s="16"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>234</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F22" s="10">
+        <v>5.5039431087518598E-3</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="I22" s="6">
+        <v>5</v>
+      </c>
+      <c r="J22" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>377</v>
+      </c>
+      <c r="L22" s="17" t="s">
+        <v>376</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N22" s="16"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>652</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F23" s="10">
+        <v>4.4700385807039094E-3</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="I23" s="6">
+        <v>8</v>
+      </c>
+      <c r="J23" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="K23" s="17" t="s">
+        <v>381</v>
+      </c>
+      <c r="L23" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N23" s="16"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>551</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F24" s="10">
+        <v>2.7839409844576937E-3</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="I24" s="6">
+        <v>5</v>
+      </c>
+      <c r="J24" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="K24" s="17" t="s">
+        <v>384</v>
+      </c>
+      <c r="L24" s="17" t="s">
         <v>383</v>
       </c>
-      <c r="H2" s="13" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+      <c r="M24" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N24" s="16"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
+        <v>552</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F25" s="10">
+        <v>2.0431194829814742E-3</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="I25" s="6">
+        <v>5</v>
+      </c>
+      <c r="J25" s="21" t="s">
+        <v>385</v>
+      </c>
+      <c r="K25" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="L25" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N25" s="16"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
+        <v>807</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F26" s="10">
+        <v>1.7718440648280807E-3</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="I26" s="6">
+        <v>5</v>
+      </c>
+      <c r="J26" s="21" t="s">
+        <v>393</v>
+      </c>
+      <c r="K26" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="L26" s="17" t="s">
+        <v>395</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N26" s="16"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
+        <v>106</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F27" s="7">
+        <v>1.4224459723031085E-2</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="I27" s="6">
+        <v>10</v>
+      </c>
+      <c r="J27" s="21" t="s">
+        <v>396</v>
+      </c>
+      <c r="K27" s="17" t="s">
+        <v>398</v>
+      </c>
+      <c r="L27" s="17" t="s">
+        <v>397</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N27" s="16"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
+        <v>243</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F28" s="7">
+        <v>1.2407844110385346E-2</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="I28" s="6">
+        <v>10</v>
+      </c>
+      <c r="J28" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="K28" s="17" t="s">
+        <v>401</v>
+      </c>
+      <c r="L28" s="17" t="s">
+        <v>400</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N28" s="16"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
+        <v>236</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F29" s="10">
+        <v>8.654823259147992E-3</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="I29" s="6">
+        <v>10</v>
+      </c>
+      <c r="J29" s="21" t="s">
+        <v>402</v>
+      </c>
+      <c r="K29" s="17" t="s">
+        <v>404</v>
+      </c>
+      <c r="L29" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N29" s="16"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
+        <v>277</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F30" s="10">
+        <v>8.2392928977464593E-3</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="I30" s="6">
+        <v>4</v>
+      </c>
+      <c r="J30" s="21" t="s">
+        <v>407</v>
+      </c>
+      <c r="K30" s="17" t="s">
+        <v>409</v>
+      </c>
+      <c r="L30" s="17" t="s">
+        <v>408</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N30" s="16"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
+        <v>858</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F31" s="10">
+        <v>5.1049684701715108E-3</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="I31" s="6">
+        <v>5</v>
+      </c>
+      <c r="J31" s="21" t="s">
+        <v>410</v>
+      </c>
+      <c r="K31" s="17" t="s">
+        <v>412</v>
+      </c>
+      <c r="L31" s="17" t="s">
+        <v>411</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N31" s="16"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
+        <v>667</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F32" s="10">
+        <v>4.7611312961400119E-3</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="I32" s="6">
+        <v>5</v>
+      </c>
+      <c r="J32" s="21" t="s">
+        <v>414</v>
+      </c>
+      <c r="K32" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="L32" s="17" t="s">
+        <v>415</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N32" s="16"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
+        <v>576</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F33" s="10">
+        <v>4.4154705511015406E-3</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="I33" s="6">
+        <v>5</v>
+      </c>
+      <c r="J33" s="21" t="s">
+        <v>417</v>
+      </c>
+      <c r="K33" s="17" t="s">
+        <v>419</v>
+      </c>
+      <c r="L33" s="17" t="s">
+        <v>418</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N33" s="16"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
+        <v>808</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F34" s="10">
+        <v>2.8538681137612394E-3</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="I34" s="6">
+        <v>5</v>
+      </c>
+      <c r="J34" s="21" t="s">
+        <v>420</v>
+      </c>
+      <c r="K34" s="17" t="s">
+        <v>422</v>
+      </c>
+      <c r="L34" s="17" t="s">
+        <v>421</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N34" s="16"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
+        <v>109</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C35" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F35" s="10">
+        <v>2.8137215642739595E-3</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="I35" s="6">
+        <v>5</v>
+      </c>
+      <c r="J35" s="21" t="s">
+        <v>423</v>
+      </c>
+      <c r="K35" s="17" t="s">
+        <v>424</v>
+      </c>
+      <c r="L35" s="17" t="s">
+        <v>425</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N35" s="16"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
+        <v>267</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="F36" s="7">
+        <v>1.6868828351766882E-2</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="I36" s="6">
+        <v>10</v>
+      </c>
+      <c r="J36" s="21" t="s">
+        <v>426</v>
+      </c>
+      <c r="K36" s="17" t="s">
+        <v>431</v>
+      </c>
+      <c r="L36" s="17" t="s">
+        <v>432</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N36" s="16"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
+        <v>138</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="F37" s="7">
+        <v>1.2742149458657334E-2</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I37" s="6">
+        <v>10</v>
+      </c>
+      <c r="J37" s="21" t="s">
+        <v>433</v>
+      </c>
+      <c r="K37" s="17" t="s">
+        <v>436</v>
+      </c>
+      <c r="L37" s="17" t="s">
+        <v>437</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N37" s="16"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
+        <v>779</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F38" s="7">
+        <v>1.4440810477971976E-2</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="I38" s="6">
+        <v>10</v>
+      </c>
+      <c r="J38" s="21" t="s">
+        <v>438</v>
+      </c>
+      <c r="K38" s="17" t="s">
+        <v>440</v>
+      </c>
+      <c r="L38" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N38" s="16"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
+        <v>262</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F39" s="7">
+        <v>1.8838172247292208E-2</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="I39" s="6">
+        <v>10</v>
+      </c>
+      <c r="J39" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="K39" s="17" t="s">
+        <v>445</v>
+      </c>
+      <c r="L39" s="17" t="s">
+        <v>446</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N39" s="16"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
+        <v>249</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F40" s="7">
+        <v>1.1735425361113359E-2</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="I40" s="6">
+        <v>10</v>
+      </c>
+      <c r="J40" s="21" t="s">
+        <v>447</v>
+      </c>
+      <c r="K40" s="17" t="s">
+        <v>449</v>
+      </c>
+      <c r="L40" s="17" t="s">
+        <v>448</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N40" s="16"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41" s="3">
+        <v>108</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C41" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F41" s="10">
+        <v>7.5133013260082855E-3</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="I41" s="6">
+        <v>8</v>
+      </c>
+      <c r="J41" s="21" t="s">
+        <v>450</v>
+      </c>
+      <c r="K41" s="17" t="s">
+        <v>453</v>
+      </c>
+      <c r="L41" s="17" t="s">
+        <v>452</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N41" s="16"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42" s="3">
+        <v>774</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="F42" s="7">
+        <v>1.2682547983570351E-2</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="I42" s="6">
+        <v>10</v>
+      </c>
+      <c r="J42" s="21" t="s">
+        <v>454</v>
+      </c>
+      <c r="K42" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="L42" s="17" t="s">
+        <v>456</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N42" s="16"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
+        <v>615</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F43" s="7">
+        <v>2.2916421048759718E-2</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="I43" s="6">
+        <v>10</v>
+      </c>
+      <c r="J43" s="22" t="s">
+        <v>458</v>
+      </c>
+      <c r="K43" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="L43" s="17" t="s">
+        <v>461</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N43" s="16"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" s="3">
+        <v>99</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C44" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F44" s="7">
+        <v>2.1965990704229194E-2</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="I44" s="6">
+        <v>10</v>
+      </c>
+      <c r="J44" s="21" t="s">
+        <v>460</v>
+      </c>
+      <c r="K44" s="17" t="s">
+        <v>464</v>
+      </c>
+      <c r="L44" s="17" t="s">
+        <v>463</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N44" s="16"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45" s="3">
+        <v>617</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F45" s="10">
+        <v>7.1122270218292359E-3</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="I45" s="6">
+        <v>8</v>
+      </c>
+      <c r="J45" s="21" t="s">
+        <v>465</v>
+      </c>
+      <c r="K45" s="17" t="s">
+        <v>469</v>
+      </c>
+      <c r="L45" s="17" t="s">
+        <v>468</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N45" s="16"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46" s="3">
+        <v>668</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C46" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="F46" s="7">
+        <v>1.3280926686582374E-2</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="I46" s="6">
+        <v>9</v>
+      </c>
+      <c r="J46" s="21" t="s">
+        <v>470</v>
+      </c>
+      <c r="K46" s="17" t="s">
+        <v>472</v>
+      </c>
+      <c r="L46" s="17" t="s">
+        <v>471</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N46" s="16"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" s="3">
+        <v>839</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C47" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F47" s="7">
+        <v>1.1655580919690624E-2</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="I47" s="6">
+        <v>10</v>
+      </c>
+      <c r="J47" s="21" t="s">
+        <v>473</v>
+      </c>
+      <c r="K47" s="17" t="s">
+        <v>475</v>
+      </c>
+      <c r="L47" s="17" t="s">
+        <v>474</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N47" s="16"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" s="3">
+        <v>52</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C48" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F48" s="7">
+        <v>9.6955214810818292E-3</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="I48" s="6">
+        <v>10</v>
+      </c>
+      <c r="J48" s="21" t="s">
+        <v>476</v>
+      </c>
+      <c r="K48" s="17" t="s">
+        <v>479</v>
+      </c>
+      <c r="L48" s="17" t="s">
+        <v>478</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N48" s="16"/>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49" s="3">
+        <v>268</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C49" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F49" s="7">
+        <v>2.0221683745483169E-2</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="I49" s="6">
+        <v>10</v>
+      </c>
+      <c r="J49" s="21" t="s">
+        <v>482</v>
+      </c>
+      <c r="K49" s="17" t="s">
+        <v>481</v>
+      </c>
+      <c r="L49" s="16">
+        <v>-100.359576893945</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N49" s="16"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50" s="3">
+        <v>186</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F50" s="7">
+        <v>1.9348457402295335E-2</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="I50" s="6">
+        <v>10</v>
+      </c>
+      <c r="J50" s="21" t="s">
+        <v>483</v>
+      </c>
+      <c r="K50" s="17" t="s">
+        <v>485</v>
+      </c>
+      <c r="L50" s="17" t="s">
+        <v>484</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N50" s="16"/>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A51" s="3">
+        <v>308</v>
+      </c>
+      <c r="B51" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C51" s="25" t="s">
+        <v>301</v>
+      </c>
+      <c r="D51" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="E51" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="F51" s="28">
+        <v>5.7260866255360509E-3</v>
+      </c>
+      <c r="G51" s="28"/>
+      <c r="H51" s="28"/>
+      <c r="I51" s="29">
+        <v>5</v>
+      </c>
+      <c r="J51" s="30"/>
+      <c r="K51" s="31" t="s">
+        <v>211</v>
+      </c>
+      <c r="L51" s="31" t="s">
+        <v>213</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="N51" s="16"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A52" s="3">
+        <v>801</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F52" s="7">
+        <v>3.9252610120436918E-2</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="I52" s="6">
+        <v>10</v>
+      </c>
+      <c r="J52" s="21" t="s">
+        <v>486</v>
+      </c>
+      <c r="K52" s="17" t="s">
+        <v>489</v>
+      </c>
+      <c r="L52" s="17" t="s">
+        <v>488</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N52" s="16"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A53" s="3">
+        <v>274</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C53" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F53" s="7">
+        <v>2.041917208193085E-2</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I53" s="6">
+        <v>10</v>
+      </c>
+      <c r="J53" s="21" t="s">
+        <v>491</v>
+      </c>
+      <c r="K53" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="L53" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N53" s="16"/>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A54" s="3">
+        <v>62</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C54" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F54" s="7">
+        <v>1.3994423922537694E-2</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="I54" s="6">
+        <v>10</v>
+      </c>
+      <c r="J54" s="21" t="s">
+        <v>493</v>
+      </c>
+      <c r="K54" s="17" t="s">
+        <v>494</v>
+      </c>
+      <c r="L54" s="17" t="s">
+        <v>495</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N54" s="16"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A55" s="3">
+        <v>255</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C55" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F55" s="7">
+        <v>1.3032183684948084E-2</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I55" s="6">
+        <v>10</v>
+      </c>
+      <c r="J55" s="21" t="s">
+        <v>496</v>
+      </c>
+      <c r="K55" s="17" t="s">
+        <v>498</v>
+      </c>
+      <c r="L55" s="17" t="s">
+        <v>497</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N55" s="16"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A56" s="3">
+        <v>90</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C56" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F56" s="7">
+        <v>1.1808211440281434E-2</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="H56" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="I56" s="6">
+        <v>10</v>
+      </c>
+      <c r="J56" s="21" t="s">
+        <v>499</v>
+      </c>
+      <c r="K56" s="17" t="s">
+        <v>501</v>
+      </c>
+      <c r="L56" s="17" t="s">
+        <v>500</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N56" s="16"/>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A57" s="3">
+        <v>153</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C57" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F57" s="7">
+        <v>1.1621296174072784E-2</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="I57" s="6">
+        <v>10</v>
+      </c>
+      <c r="J57" s="21" t="s">
+        <v>502</v>
+      </c>
+      <c r="K57" s="17" t="s">
+        <v>504</v>
+      </c>
+      <c r="L57" s="17" t="s">
+        <v>503</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N57" s="16"/>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A58" s="3">
+        <v>199</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C58" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F58" s="7">
+        <v>1.0391030746663709E-2</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="H58" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="I58" s="6">
+        <v>10</v>
+      </c>
+      <c r="J58" s="21" t="s">
+        <v>505</v>
+      </c>
+      <c r="K58" s="17" t="s">
+        <v>507</v>
+      </c>
+      <c r="L58" s="17" t="s">
+        <v>506</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N58" s="16"/>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A59" s="3">
+        <v>47</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C59" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F59" s="10">
+        <v>9.2103343959954471E-3</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I59" s="6">
+        <v>10</v>
+      </c>
+      <c r="J59" s="21" t="s">
+        <v>508</v>
+      </c>
+      <c r="K59" s="17" t="s">
+        <v>509</v>
+      </c>
+      <c r="L59" s="16">
+        <v>-86.822608058303601</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N59" s="16"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A60" s="3">
+        <v>58</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C60" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F60" s="10">
+        <v>8.4847454642151248E-3</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="I60" s="6">
+        <v>9</v>
+      </c>
+      <c r="J60" s="21" t="s">
+        <v>510</v>
+      </c>
+      <c r="K60" s="17" t="s">
+        <v>512</v>
+      </c>
+      <c r="L60" s="17" t="s">
+        <v>511</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N60" s="16"/>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A61" s="3">
+        <v>651</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C61" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F61" s="10">
+        <v>8.357851542356241E-3</v>
+      </c>
+      <c r="G61" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="I61" s="6">
+        <v>10</v>
+      </c>
+      <c r="J61" s="21" t="s">
+        <v>513</v>
+      </c>
+      <c r="K61" s="17" t="s">
+        <v>515</v>
+      </c>
+      <c r="L61" s="17" t="s">
+        <v>514</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N61" s="16"/>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A62" s="3">
+        <v>665</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C62" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F62" s="7">
+        <v>7.9611433347388412E-3</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I62" s="6">
+        <v>10</v>
+      </c>
+      <c r="J62" s="21" t="s">
+        <v>516</v>
+      </c>
+      <c r="K62" s="17" t="s">
+        <v>518</v>
+      </c>
+      <c r="L62" s="17" t="s">
+        <v>517</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N62" s="16"/>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A63" s="3">
+        <v>723</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C63" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F63" s="10">
+        <v>6.003833613320503E-3</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="H63" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="I63" s="6">
+        <v>7</v>
+      </c>
+      <c r="J63" s="21" t="s">
+        <v>519</v>
+      </c>
+      <c r="K63" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="L63" s="17" t="s">
+        <v>521</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N63" s="16"/>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A64" s="3">
+        <v>86</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C64" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F64" s="10">
+        <v>5.2416647144758709E-3</v>
+      </c>
+      <c r="G64" t="s">
+        <v>527</v>
+      </c>
+      <c r="H64" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="I64" s="6">
+        <v>1</v>
+      </c>
+      <c r="J64" s="21" t="s">
+        <v>523</v>
+      </c>
+      <c r="K64" s="17" t="s">
+        <v>526</v>
+      </c>
+      <c r="L64" s="17" t="s">
+        <v>525</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N64" s="16"/>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A65" s="3">
+        <v>663</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C65" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F65" s="10">
+        <v>4.6460817791641618E-3</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="H65" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="I65" s="6">
+        <v>3</v>
+      </c>
+      <c r="J65" s="21" t="s">
+        <v>528</v>
+      </c>
+      <c r="K65" s="17" t="s">
+        <v>530</v>
+      </c>
+      <c r="L65" s="17" t="s">
+        <v>529</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N65" s="16"/>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A66" s="3">
+        <v>69</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C66" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F66" s="10">
+        <v>3.7817545239335749E-3</v>
+      </c>
+      <c r="G66" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="H66" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="I66" s="6">
+        <v>4</v>
+      </c>
+      <c r="J66" s="21" t="s">
+        <v>533</v>
+      </c>
+      <c r="K66" s="17" t="s">
+        <v>532</v>
+      </c>
+      <c r="L66" s="17" t="s">
+        <v>531</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N66" s="16"/>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A67" s="3">
+        <v>251</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C67" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F67" s="7">
+        <v>9.9398063169533236E-3</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="H67" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="I67" s="6">
+        <v>10</v>
+      </c>
+      <c r="J67" s="21" t="s">
+        <v>534</v>
+      </c>
+      <c r="K67" s="17" t="s">
+        <v>536</v>
+      </c>
+      <c r="L67" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N67" s="16"/>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A68" s="3">
+        <v>24</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C68" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="F68" s="7">
+        <v>1.6640500941968742E-2</v>
+      </c>
+      <c r="G68" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H68" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="I68" s="6">
+        <v>10</v>
+      </c>
+      <c r="J68" s="21" t="s">
+        <v>537</v>
+      </c>
+      <c r="K68" s="17" t="s">
+        <v>539</v>
+      </c>
+      <c r="L68" s="17" t="s">
+        <v>538</v>
+      </c>
+      <c r="M68" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N68" s="16"/>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69" s="3">
+        <v>322</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C69" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F69" s="7">
+        <v>1.2340350340891489E-2</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H69" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="I69" s="6">
+        <v>8</v>
+      </c>
+      <c r="J69" s="21" t="s">
+        <v>540</v>
+      </c>
+      <c r="K69" s="17" t="s">
+        <v>542</v>
+      </c>
+      <c r="L69" s="17" t="s">
+        <v>541</v>
+      </c>
+      <c r="M69" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N69" s="16"/>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A70" s="3">
+        <v>812</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C70" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E70" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="F70" s="7">
+        <v>1.1033720708268059E-2</v>
+      </c>
+      <c r="G70" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H70" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="I70" s="6">
+        <v>10</v>
+      </c>
+      <c r="J70" s="21" t="s">
+        <v>543</v>
+      </c>
+      <c r="K70" s="17" t="s">
+        <v>545</v>
+      </c>
+      <c r="L70" s="17" t="s">
+        <v>544</v>
+      </c>
+      <c r="M70" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N70" s="16"/>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A71" s="3">
+        <v>789</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E71" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F71" s="7">
+        <v>2.2300002624919185E-2</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I71" s="6">
+        <v>10</v>
+      </c>
+      <c r="J71" s="21" t="s">
+        <v>546</v>
+      </c>
+      <c r="K71" s="17" t="s">
+        <v>548</v>
+      </c>
+      <c r="L71" s="17" t="s">
+        <v>547</v>
+      </c>
+      <c r="M71" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N71" s="16"/>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A72" s="3">
+        <v>59</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C72" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F72" s="7">
+        <v>1.7395490781259557E-2</v>
+      </c>
+      <c r="G72" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="H72" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="I72" s="6">
+        <v>10</v>
+      </c>
+      <c r="J72" s="21" t="s">
+        <v>549</v>
+      </c>
+      <c r="K72" s="17" t="s">
+        <v>550</v>
+      </c>
+      <c r="L72" s="17" t="s">
+        <v>551</v>
+      </c>
+      <c r="M72" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N72" s="16"/>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A73" s="3">
+        <v>821</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C73" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F73" s="7">
+        <v>9.3069760799181535E-3</v>
+      </c>
+      <c r="G73" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="H73" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="I73" s="6">
+        <v>5</v>
+      </c>
+      <c r="J73" s="21" t="s">
+        <v>553</v>
+      </c>
+      <c r="K73" s="17" t="s">
+        <v>556</v>
+      </c>
+      <c r="L73" s="17" t="s">
+        <v>555</v>
+      </c>
+      <c r="M73" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N73" s="16"/>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A74" s="3">
+        <v>139</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C74" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E74" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F74" s="10">
+        <v>6.7852963838663195E-3</v>
+      </c>
+      <c r="G74" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="H74" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="I74" s="6">
+        <v>9</v>
+      </c>
+      <c r="J74" s="21" t="s">
+        <v>557</v>
+      </c>
+      <c r="K74" s="17" t="s">
+        <v>559</v>
+      </c>
+      <c r="L74" s="17" t="s">
+        <v>558</v>
+      </c>
+      <c r="M74" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N74" s="16"/>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A75" s="3">
+        <v>270</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C75" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E75" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F75" s="10">
+        <v>3.76686701981193E-3</v>
+      </c>
+      <c r="G75" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="H75" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="I75" s="6">
+        <v>4</v>
+      </c>
+      <c r="J75" s="21" t="s">
+        <v>560</v>
+      </c>
+      <c r="K75" s="17" t="s">
+        <v>562</v>
+      </c>
+      <c r="L75" s="17" t="s">
+        <v>561</v>
+      </c>
+      <c r="M75" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N75" s="16"/>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A76" s="3">
+        <v>78</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C76" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E76" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F76" s="7">
+        <v>2.8127862242819213E-2</v>
+      </c>
+      <c r="G76" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="H76" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="I76" s="6">
+        <v>10</v>
+      </c>
+      <c r="J76" s="21" t="s">
+        <v>563</v>
+      </c>
+      <c r="K76" s="17" t="s">
+        <v>565</v>
+      </c>
+      <c r="L76" s="17" t="s">
+        <v>564</v>
+      </c>
+      <c r="M76" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N76" s="16"/>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A77" s="3">
+        <v>253</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C77" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F77" s="7">
+        <v>2.1636851085154972E-2</v>
+      </c>
+      <c r="G77" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="H77" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="I77" s="6">
+        <v>10</v>
+      </c>
+      <c r="J77" s="21" t="s">
+        <v>567</v>
+      </c>
+      <c r="K77" s="17" t="s">
+        <v>569</v>
+      </c>
+      <c r="L77" s="17" t="s">
+        <v>568</v>
+      </c>
+      <c r="M77" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N77" s="16"/>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A78" s="3">
+        <v>281</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C78" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E78" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F78" s="7">
+        <v>1.7871180555153451E-2</v>
+      </c>
+      <c r="G78" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="H78" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="I78" s="6">
+        <v>7</v>
+      </c>
+      <c r="J78" s="21" t="s">
+        <v>570</v>
+      </c>
+      <c r="K78" s="17" t="s">
+        <v>572</v>
+      </c>
+      <c r="L78" s="17" t="s">
+        <v>571</v>
+      </c>
+      <c r="M78" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N78" s="16"/>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A79" s="3">
+        <v>135</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C79" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F79" s="7">
+        <v>1.1572256224504493E-2</v>
+      </c>
+      <c r="G79" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="H79" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="I79" s="6">
+        <v>8</v>
+      </c>
+      <c r="J79" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="K79" s="17" t="s">
+        <v>575</v>
+      </c>
+      <c r="L79" s="17" t="s">
+        <v>574</v>
+      </c>
+      <c r="M79" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="N79" s="16"/>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A80" s="12">
+        <v>131</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C80" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F80" s="7">
+        <v>2.1213529829138978E-2</v>
+      </c>
+      <c r="G80" s="7"/>
+      <c r="H80" s="7"/>
+      <c r="I80" s="6">
+        <v>10</v>
+      </c>
+      <c r="J80" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="K80" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="L80" s="18" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A81" s="12">
+        <v>375</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C81" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F81" s="7">
+        <v>2.1210471293309406E-2</v>
+      </c>
+      <c r="G81" s="7"/>
+      <c r="H81" s="7"/>
+      <c r="I81" s="6">
+        <v>9</v>
+      </c>
+      <c r="J81" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="K81" s="18">
+        <v>19.548992839452801</v>
+      </c>
+      <c r="L81" s="18" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A82" s="12">
+        <v>451</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C82" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="F82" s="7">
+        <v>2.0763704847612412E-2</v>
+      </c>
+      <c r="G82" s="7"/>
+      <c r="H82" s="7"/>
+      <c r="I82" s="6">
+        <v>10</v>
+      </c>
+      <c r="J82" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="K82" s="18" t="s">
+        <v>256</v>
+      </c>
+      <c r="L82" s="18" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A83" s="12">
+        <v>458</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C83" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F83" s="7">
+        <v>1.8602455344606129E-2</v>
+      </c>
+      <c r="G83" s="7"/>
+      <c r="H83" s="7"/>
+      <c r="I83" s="6">
+        <v>10</v>
+      </c>
+      <c r="J83" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="K83" s="18" t="s">
+        <v>258</v>
+      </c>
+      <c r="L83" s="18" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A84" s="12">
+        <v>443</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C84" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F84" s="7">
+        <v>1.8247361781621681E-2</v>
+      </c>
+      <c r="G84" s="7"/>
+      <c r="H84" s="7"/>
+      <c r="I84" s="6">
+        <v>9</v>
+      </c>
+      <c r="J84" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="K84" s="18">
+        <v>22.129746078133198</v>
+      </c>
+      <c r="L84" s="18" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A85" s="12">
+        <v>455</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C85" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F85" s="7">
+        <v>1.8203778869464636E-2</v>
+      </c>
+      <c r="G85" s="7"/>
+      <c r="H85" s="7"/>
+      <c r="I85" s="6">
+        <v>11</v>
+      </c>
+      <c r="J85" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="K85" s="18">
+        <v>19.506940269783399</v>
+      </c>
+      <c r="L85" s="18" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A86" s="12">
+        <v>446</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C86" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F86" s="7">
+        <v>1.7755035386207405E-2</v>
+      </c>
+      <c r="G86" s="7"/>
+      <c r="H86" s="7"/>
+      <c r="I86" s="6">
+        <v>10</v>
+      </c>
+      <c r="J86" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="K86" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="L86" s="18" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A87" s="12">
+        <v>346</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C87" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F87" s="7">
+        <v>1.7132743239494368E-2</v>
+      </c>
+      <c r="G87" s="7"/>
+      <c r="H87" s="7"/>
+      <c r="I87" s="6">
+        <v>7</v>
+      </c>
+      <c r="J87" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="K87" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="L87" s="18" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A88" s="12">
+        <v>445</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C88" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F88" s="7">
+        <v>1.6345485904277618E-2</v>
+      </c>
+      <c r="G88" s="7"/>
+      <c r="H88" s="7"/>
+      <c r="I88" s="6">
+        <v>8</v>
+      </c>
+      <c r="J88" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="K88" s="18" t="s">
+        <v>266</v>
+      </c>
+      <c r="L88" s="18" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A89" s="12">
+        <v>400</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C89" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F89" s="10">
+        <v>1.6172671289420907E-2</v>
+      </c>
+      <c r="G89" s="10"/>
+      <c r="H89" s="10"/>
+      <c r="I89" s="6">
+        <v>9</v>
+      </c>
+      <c r="J89" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="K89" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="L89" s="18">
+        <v>-99.179037170726104</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A90" s="12">
+        <v>76</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C90" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F90" s="10">
+        <v>1.5680281276461372E-2</v>
+      </c>
+      <c r="G90" s="10"/>
+      <c r="H90" s="10"/>
+      <c r="I90" s="6">
+        <v>10</v>
+      </c>
+      <c r="J90" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="K90" s="18" t="s">
+        <v>269</v>
+      </c>
+      <c r="L90" s="18" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A91" s="12">
+        <v>107</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C91" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="F91" s="7">
+        <v>1.4652280469027492E-2</v>
+      </c>
+      <c r="G91" s="7" t="s">
+        <v>524</v>
+      </c>
+      <c r="H91" s="7" t="s">
+        <v>524</v>
+      </c>
+      <c r="I91" s="6">
+        <v>9</v>
+      </c>
+      <c r="J91" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="K91" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="L91" s="18" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A92" s="12">
+        <v>459</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C92" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F92" s="10">
+        <v>1.3350039104971016E-2</v>
+      </c>
+      <c r="G92" s="10" t="s">
+        <v>579</v>
+      </c>
+      <c r="H92" s="10" t="s">
+        <v>579</v>
+      </c>
+      <c r="I92" s="6">
+        <v>11</v>
+      </c>
+      <c r="J92" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="K92" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="L92" s="18" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A93" s="12">
+        <v>153</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C93" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F93" s="10">
+        <v>1.2999251960434605E-2</v>
+      </c>
+      <c r="G93" s="10" t="s">
+        <v>579</v>
+      </c>
+      <c r="H93" s="10" t="s">
+        <v>579</v>
+      </c>
+      <c r="I93" s="6">
+        <v>9</v>
+      </c>
+      <c r="J93" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="K93" s="18">
+        <v>23.0440959197166</v>
+      </c>
+      <c r="L93" s="18" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A94" s="12">
+        <v>432</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C94" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F94" s="10">
+        <v>1.2634067676041234E-2</v>
+      </c>
+      <c r="G94" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="H94" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="I94" s="6">
+        <v>10</v>
+      </c>
+      <c r="J94" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="K94" s="18">
+        <v>19.272015139846602</v>
+      </c>
+      <c r="L94" s="18" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A95" s="12">
+        <v>377</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C95" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F95" s="10">
+        <v>1.2373729999885532E-2</v>
+      </c>
+      <c r="G95" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="H95" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="I95" s="6">
+        <v>11</v>
+      </c>
+      <c r="J95" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E3" s="7">
-        <v>1.3838290082880884E-2</v>
-      </c>
-      <c r="F3" s="6">
+      <c r="K95" s="18">
+        <v>19.419052005461999</v>
+      </c>
+      <c r="L95" s="18">
+        <v>-99.214334110229004</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A96" s="12">
+        <v>317</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C96" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F96" s="10">
+        <v>1.2057633992142438E-2</v>
+      </c>
+      <c r="G96" s="10" t="s">
+        <v>580</v>
+      </c>
+      <c r="H96" s="10" t="s">
+        <v>580</v>
+      </c>
+      <c r="I96" s="6">
+        <v>9</v>
+      </c>
+      <c r="J96" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="K96" s="18">
+        <v>20.897403003383801</v>
+      </c>
+      <c r="L96" s="18" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A97" s="12">
+        <v>422</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C97" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F97" s="10">
+        <v>1.0854988342011422E-2</v>
+      </c>
+      <c r="G97" s="10" t="s">
+        <v>477</v>
+      </c>
+      <c r="H97" s="10" t="s">
+        <v>477</v>
+      </c>
+      <c r="I97" s="6">
+        <v>9</v>
+      </c>
+      <c r="J97" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="K97" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="L97" s="18" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A98" s="12">
+        <v>305</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C98" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F98" s="10">
+        <v>1.0355047415795852E-2</v>
+      </c>
+      <c r="G98" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="H98" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="I98" s="6">
+        <v>11</v>
+      </c>
+      <c r="J98" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="K98" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="L98" s="18" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A99" s="12">
+        <v>449</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C99" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F99" s="10">
+        <v>9.5218141699890037E-3</v>
+      </c>
+      <c r="G99" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="H99" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="I99" s="6">
+        <v>11</v>
+      </c>
+      <c r="J99" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="K99" s="18">
+        <v>19.3884836634716</v>
+      </c>
+      <c r="L99" s="18" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A100" s="12">
+        <v>427</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C100" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F100" s="10">
+        <v>8.5153846040539136E-3</v>
+      </c>
+      <c r="G100" s="10" t="s">
+        <v>579</v>
+      </c>
+      <c r="H100" s="10" t="s">
+        <v>581</v>
+      </c>
+      <c r="I100" s="6">
         <v>10</v>
       </c>
-      <c r="G3" s="17">
-        <v>20.635167632902299</v>
-      </c>
-      <c r="H3" s="17" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>127</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="9" t="s">
+      <c r="J100" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="K100" s="18" t="s">
+        <v>283</v>
+      </c>
+      <c r="L100" s="18" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A101" s="12">
+        <v>398</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C101" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E101" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="E4" s="7">
-        <v>2.159342568746472E-2</v>
-      </c>
-      <c r="F4" s="6">
+      <c r="F101" s="10">
+        <v>8.1803746107407555E-3</v>
+      </c>
+      <c r="G101" s="10" t="s">
+        <v>579</v>
+      </c>
+      <c r="H101" s="10" t="s">
+        <v>581</v>
+      </c>
+      <c r="I101" s="6">
+        <v>9</v>
+      </c>
+      <c r="J101" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="K101" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="L101" s="18" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A102" s="12">
+        <v>453</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C102" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F102" s="10">
+        <v>8.1301069626745995E-3</v>
+      </c>
+      <c r="G102" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="H102" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="I102" s="6">
+        <v>5</v>
+      </c>
+      <c r="J102" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="K102" s="18">
+        <v>20.6076550152689</v>
+      </c>
+      <c r="L102" s="18" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A103" s="12">
+        <v>435</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C103" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F103" s="10">
+        <v>7.7415456772286593E-3</v>
+      </c>
+      <c r="G103" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="H103" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="I103" s="6">
         <v>10</v>
       </c>
-      <c r="G4" s="17">
-        <v>19.3737772199127</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
-        <v>333</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="9" t="s">
+      <c r="J103" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="K103" s="18">
+        <v>19.417376983685099</v>
+      </c>
+      <c r="L103" s="18" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A104" s="12">
+        <v>421</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C104" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E104" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="E5" s="10">
-        <v>7.8252122337391823E-3</v>
-      </c>
-      <c r="F5" s="6">
-        <v>5</v>
-      </c>
-      <c r="G5" s="17">
-        <v>19.439728238856599</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
-        <v>178</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="E6" s="10">
-        <v>6.0846674247843667E-3</v>
-      </c>
-      <c r="F6" s="6">
-        <v>10</v>
-      </c>
-      <c r="G6" s="17">
-        <v>19.483357451547398</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
-        <v>802</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="E7" s="10">
-        <v>5.0952928104922666E-3</v>
-      </c>
-      <c r="F7" s="6">
-        <v>10</v>
-      </c>
-      <c r="G7" s="17">
-        <v>19.360158749106301</v>
-      </c>
-      <c r="H7" s="17" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
-        <v>126</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E8" s="10">
-        <v>4.2220204530022372E-3</v>
-      </c>
-      <c r="F8" s="6">
-        <v>10</v>
-      </c>
-      <c r="G8" s="17">
-        <v>19.4406397466078</v>
-      </c>
-      <c r="H8" s="17" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
-        <v>330</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="E9" s="10">
-        <v>3.7043088476581844E-3</v>
-      </c>
-      <c r="F9" s="6">
-        <v>7</v>
-      </c>
-      <c r="G9" s="17">
-        <v>21.030234633725399</v>
-      </c>
-      <c r="H9" s="17" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
-        <v>334</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="E10" s="10">
-        <v>1.8709650274066469E-3</v>
-      </c>
-      <c r="F10" s="6">
-        <v>7</v>
-      </c>
-      <c r="G10" s="17">
-        <v>15.7627981727008</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
-        <v>13</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1.12892803485364E-2</v>
-      </c>
-      <c r="F11" s="6">
-        <v>10</v>
-      </c>
-      <c r="G11" s="17">
-        <v>19.160982142306299</v>
-      </c>
-      <c r="H11" s="17" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
-        <v>235</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="F104" s="10">
+        <v>7.4367050813383831E-3</v>
+      </c>
+      <c r="G104" s="10" t="s">
+        <v>579</v>
+      </c>
+      <c r="H104" s="10" t="s">
+        <v>579</v>
+      </c>
+      <c r="I104" s="6">
+        <v>9</v>
+      </c>
+      <c r="J104" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="K104" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="L104" s="18" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A105" s="12">
+        <v>429</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C105" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F105" s="10">
+        <v>5.6402679447685958E-3</v>
+      </c>
+      <c r="G105" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="H105" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="I105" s="6">
+        <v>9</v>
+      </c>
+      <c r="J105" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="K105" s="18">
+        <v>20.643285180687901</v>
+      </c>
+      <c r="L105" s="18" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A106" s="12">
+        <v>137</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C106" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E106" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E12" s="7">
-        <v>3.5985967166643498E-2</v>
-      </c>
-      <c r="F12" s="6">
-        <v>10</v>
-      </c>
-      <c r="G12" s="17">
-        <v>17.078444795390698</v>
-      </c>
-      <c r="H12" s="17" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
-        <v>182</v>
-      </c>
-      <c r="B13" s="8" t="s">
+      <c r="F106" s="10">
+        <v>4.9108683201326657E-3</v>
+      </c>
+      <c r="G106" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="H106" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="I106" s="6">
         <v>9</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E13" s="7">
-        <v>3.5644074373929843E-2</v>
-      </c>
-      <c r="F13" s="6">
-        <v>10</v>
-      </c>
-      <c r="G13" s="17">
-        <v>21.080473013899201</v>
-      </c>
-      <c r="H13" s="17">
-        <v>-89.637514817489006</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
-        <v>174</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E14" s="7">
-        <v>3.0428341835977236E-2</v>
-      </c>
-      <c r="F14" s="6">
-        <v>10</v>
-      </c>
-      <c r="G14" s="17">
-        <v>24.143290092761301</v>
-      </c>
-      <c r="H14" s="17" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
-        <v>98</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E15" s="7">
-        <v>2.8799763282912907E-2</v>
-      </c>
-      <c r="F15" s="6">
-        <v>10</v>
-      </c>
-      <c r="G15" s="17">
-        <v>19.304151401350701</v>
-      </c>
-      <c r="H15" s="17" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
-        <v>232</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E16" s="7">
-        <v>2.8733897314624928E-2</v>
-      </c>
-      <c r="F16" s="6">
-        <v>10</v>
-      </c>
-      <c r="G16" s="17">
-        <v>21.098175758086601</v>
-      </c>
-      <c r="H16" s="17" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
-        <v>233</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E17" s="7">
-        <v>2.1515404807174253E-2</v>
-      </c>
-      <c r="F17" s="6">
-        <v>10</v>
-      </c>
-      <c r="G17" s="17">
-        <v>20.571180976978201</v>
-      </c>
-      <c r="H17" s="17" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
-        <v>177</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E18" s="7">
-        <v>2.0063778202674572E-2</v>
-      </c>
-      <c r="F18" s="6">
-        <v>10</v>
-      </c>
-      <c r="G18" s="17">
-        <v>19.335085018669801</v>
-      </c>
-      <c r="H18" s="17" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
-        <v>814</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E19" s="7">
-        <v>1.1317007292279867E-2</v>
-      </c>
-      <c r="F19" s="6">
-        <v>8</v>
-      </c>
-      <c r="G19" s="17">
-        <v>20.690843274102502</v>
-      </c>
-      <c r="H19" s="17" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
-        <v>587</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E20" s="10">
-        <v>9.8573962791872784E-3</v>
-      </c>
-      <c r="F20" s="6">
-        <v>5</v>
-      </c>
-      <c r="G20" s="17">
-        <v>20.6794210179198</v>
-      </c>
-      <c r="H20" s="17" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
-        <v>819</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E21" s="10">
-        <v>6.4709636133180506E-3</v>
-      </c>
-      <c r="F21" s="6">
-        <v>5</v>
-      </c>
-      <c r="G21" s="17">
-        <v>21.0207824518371</v>
-      </c>
-      <c r="H21" s="17" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
-        <v>890</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E22" s="10">
-        <v>5.9978222327954078E-3</v>
-      </c>
-      <c r="F22" s="6">
-        <v>4</v>
-      </c>
-      <c r="G22" s="17">
-        <v>19.521060385894899</v>
-      </c>
-      <c r="H22" s="17" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
-        <v>234</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E23" s="10">
-        <v>5.5039431087518598E-3</v>
-      </c>
-      <c r="F23" s="6">
-        <v>5</v>
-      </c>
-      <c r="G23" s="17">
-        <v>20.5188249398038</v>
-      </c>
-      <c r="H23" s="17" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
-        <v>652</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E24" s="10">
-        <v>4.4700385807039094E-3</v>
-      </c>
-      <c r="F24" s="6">
-        <v>8</v>
-      </c>
-      <c r="G24" s="17">
-        <v>20.518774431886101</v>
-      </c>
-      <c r="H24" s="17">
-        <v>-100.79641878081</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
-        <v>551</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E25" s="10">
-        <v>2.7839409844576937E-3</v>
-      </c>
-      <c r="F25" s="6">
-        <v>5</v>
-      </c>
-      <c r="G25" s="17">
-        <v>20.037051119660902</v>
-      </c>
-      <c r="H25" s="17">
-        <v>-98.796809510560706</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
-        <v>552</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E26" s="10">
-        <v>2.0431194829814742E-3</v>
-      </c>
-      <c r="F26" s="6">
-        <v>5</v>
-      </c>
-      <c r="G26" s="17">
-        <v>19.454191126902099</v>
-      </c>
-      <c r="H26" s="17">
-        <v>-99.219045698697201</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
-        <v>807</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E27" s="10">
-        <v>1.7718440648280807E-3</v>
-      </c>
-      <c r="F27" s="6">
-        <v>5</v>
-      </c>
-      <c r="G27" s="17">
-        <v>20.625453982332498</v>
-      </c>
-      <c r="H27" s="17">
-        <v>-87.084673098938694</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
-        <v>106</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="9" t="s">
+      <c r="J106" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="K106" s="18">
+        <v>19.3827979499045</v>
+      </c>
+      <c r="L106" s="18" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A107" s="12">
+        <v>14</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C107" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E107" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E28" s="7">
-        <v>1.4224459723031085E-2</v>
-      </c>
-      <c r="F28" s="6">
-        <v>10</v>
-      </c>
-      <c r="G28" s="17">
-        <v>21.9264260226741</v>
-      </c>
-      <c r="H28" s="17">
-        <v>-102.295494557214</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
-        <v>243</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="9" t="s">
+      <c r="F107" s="10">
+        <v>3.8276328024454062E-3</v>
+      </c>
+      <c r="G107" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="H107" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="I107" s="6">
+        <v>9</v>
+      </c>
+      <c r="J107" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="K107" s="18" t="s">
+        <v>577</v>
+      </c>
+      <c r="L107" s="18" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A108" s="12">
+        <v>424</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C108" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E108" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E29" s="7">
-        <v>1.2407844110385346E-2</v>
-      </c>
-      <c r="F29" s="6">
-        <v>10</v>
-      </c>
-      <c r="G29" s="17">
-        <v>19.0059329479021</v>
-      </c>
-      <c r="H29" s="17" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="3">
-        <v>236</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="9" t="s">
+      <c r="F108" s="10">
+        <v>2.6571482682694911E-3</v>
+      </c>
+      <c r="G108" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="H108" s="10" t="s">
+        <v>578</v>
+      </c>
+      <c r="I108" s="6">
+        <v>1</v>
+      </c>
+      <c r="J108" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="K108" s="18">
+        <v>19.165077004486399</v>
+      </c>
+      <c r="L108" s="18" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A109" s="12">
+        <v>376</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C109" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E109" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E30" s="10">
-        <v>8.654823259147992E-3</v>
-      </c>
-      <c r="F30" s="6">
-        <v>10</v>
-      </c>
-      <c r="G30" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="H30" s="17" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
-        <v>277</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="E31" s="10">
-        <v>8.2392928977464593E-3</v>
-      </c>
-      <c r="F31" s="6">
-        <v>4</v>
-      </c>
-      <c r="G31" s="17">
-        <v>16.7712942829843</v>
-      </c>
-      <c r="H31" s="17" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="3">
-        <v>858</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="E32" s="10">
-        <v>5.1049684701715108E-3</v>
-      </c>
-      <c r="F32" s="6">
-        <v>5</v>
-      </c>
-      <c r="G32" s="17" t="s">
-        <v>235</v>
-      </c>
-      <c r="H32" s="17" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3">
-        <v>667</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="E33" s="10">
-        <v>4.7611312961400119E-3</v>
-      </c>
-      <c r="F33" s="6">
-        <v>5</v>
-      </c>
-      <c r="G33" s="17">
-        <v>19.2587351337631</v>
-      </c>
-      <c r="H33" s="17" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="3">
-        <v>576</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="E34" s="10">
-        <v>4.4154705511015406E-3</v>
-      </c>
-      <c r="F34" s="6">
-        <v>5</v>
-      </c>
-      <c r="G34" s="17" t="s">
-        <v>385</v>
-      </c>
-      <c r="H34" s="17" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="3">
-        <v>808</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="E35" s="10">
-        <v>2.8538681137612394E-3</v>
-      </c>
-      <c r="F35" s="6">
-        <v>5</v>
-      </c>
-      <c r="G35" s="17" t="s">
-        <v>238</v>
-      </c>
-      <c r="H35" s="17" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="3">
-        <v>109</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="E36" s="10">
-        <v>2.8137215642739595E-3</v>
-      </c>
-      <c r="F36" s="6">
-        <v>5</v>
-      </c>
-      <c r="G36" s="17" t="s">
-        <v>239</v>
-      </c>
-      <c r="H36" s="17" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="3">
-        <v>267</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="E37" s="7">
-        <v>1.6868828351766882E-2</v>
-      </c>
-      <c r="F37" s="6">
-        <v>10</v>
-      </c>
-      <c r="G37" s="17" t="s">
-        <v>240</v>
-      </c>
-      <c r="H37" s="17" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="3">
-        <v>138</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="E38" s="7">
-        <v>1.2742149458657334E-2</v>
-      </c>
-      <c r="F38" s="6">
-        <v>10</v>
-      </c>
-      <c r="G38" s="17" t="s">
-        <v>241</v>
-      </c>
-      <c r="H38" s="17" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="3">
-        <v>779</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E39" s="7">
-        <v>1.4440810477971976E-2</v>
-      </c>
-      <c r="F39" s="6">
-        <v>10</v>
-      </c>
-      <c r="G39" s="17" t="s">
-        <v>242</v>
-      </c>
-      <c r="H39" s="17" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="3">
-        <v>262</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E40" s="7">
-        <v>1.8838172247292208E-2</v>
-      </c>
-      <c r="F40" s="6">
-        <v>10</v>
-      </c>
-      <c r="G40" s="17" t="s">
-        <v>243</v>
-      </c>
-      <c r="H40" s="17" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="3">
-        <v>249</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="E41" s="7">
-        <v>1.1735425361113359E-2</v>
-      </c>
-      <c r="F41" s="6">
-        <v>10</v>
-      </c>
-      <c r="G41" s="17" t="s">
-        <v>244</v>
-      </c>
-      <c r="H41" s="17" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="3">
-        <v>108</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="E42" s="10">
-        <v>7.5133013260082855E-3</v>
-      </c>
-      <c r="F42" s="6">
-        <v>8</v>
-      </c>
-      <c r="G42" s="17" t="s">
-        <v>245</v>
-      </c>
-      <c r="H42" s="17" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="3">
-        <v>774</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="E43" s="7">
-        <v>1.2682547983570351E-2</v>
-      </c>
-      <c r="F43" s="6">
-        <v>10</v>
-      </c>
-      <c r="G43" s="17" t="s">
-        <v>246</v>
-      </c>
-      <c r="H43" s="17" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="3">
-        <v>615</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E44" s="7">
-        <v>2.2916421048759718E-2</v>
-      </c>
-      <c r="F44" s="6">
-        <v>10</v>
-      </c>
-      <c r="G44" s="17" t="s">
-        <v>247</v>
-      </c>
-      <c r="H44" s="17" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="3">
-        <v>99</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E45" s="7">
-        <v>2.1965990704229194E-2</v>
-      </c>
-      <c r="F45" s="6">
-        <v>10</v>
-      </c>
-      <c r="G45" s="17" t="s">
-        <v>248</v>
-      </c>
-      <c r="H45" s="17" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="3">
-        <v>617</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E46" s="10">
-        <v>7.1122270218292359E-3</v>
-      </c>
-      <c r="F46" s="6">
-        <v>8</v>
-      </c>
-      <c r="G46" s="17" t="s">
-        <v>249</v>
-      </c>
-      <c r="H46" s="17" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="3">
-        <v>668</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E47" s="7">
-        <v>1.3280926686582374E-2</v>
-      </c>
-      <c r="F47" s="6">
-        <v>9</v>
-      </c>
-      <c r="G47" s="17" t="s">
-        <v>250</v>
-      </c>
-      <c r="H47" s="17" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="3">
-        <v>839</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E48" s="7">
-        <v>1.1655580919690624E-2</v>
-      </c>
-      <c r="F48" s="6">
-        <v>10</v>
-      </c>
-      <c r="G48" s="17" t="s">
-        <v>251</v>
-      </c>
-      <c r="H48" s="17" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="3">
-        <v>52</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E49" s="7">
-        <v>9.6955214810818292E-3</v>
-      </c>
-      <c r="F49" s="6">
-        <v>10</v>
-      </c>
-      <c r="G49" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="H49" s="17" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="3">
-        <v>268</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E50" s="7">
-        <v>2.0221683745483169E-2</v>
-      </c>
-      <c r="F50" s="6">
-        <v>10</v>
-      </c>
-      <c r="G50" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="H50" s="17" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="3">
-        <v>186</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E51" s="7">
-        <v>1.9348457402295335E-2</v>
-      </c>
-      <c r="F51" s="6">
-        <v>10</v>
-      </c>
-      <c r="G51" s="17" t="s">
-        <v>254</v>
-      </c>
-      <c r="H51" s="17" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="3">
-        <v>308</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E52" s="10">
-        <v>5.7260866255360509E-3</v>
-      </c>
-      <c r="F52" s="6">
-        <v>5</v>
-      </c>
-      <c r="G52" s="17" t="s">
-        <v>255</v>
-      </c>
-      <c r="H52" s="17" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="3">
-        <v>801</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E53" s="7">
-        <v>3.9252610120436918E-2</v>
-      </c>
-      <c r="F53" s="6">
-        <v>10</v>
-      </c>
-      <c r="G53" s="17" t="s">
-        <v>256</v>
-      </c>
-      <c r="H53" s="17" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="3">
-        <v>274</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E54" s="7">
-        <v>2.041917208193085E-2</v>
-      </c>
-      <c r="F54" s="6">
-        <v>10</v>
-      </c>
-      <c r="G54" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="H54" s="17" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="3">
-        <v>62</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D55" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E55" s="7">
-        <v>1.3994423922537694E-2</v>
-      </c>
-      <c r="F55" s="6">
-        <v>10</v>
-      </c>
-      <c r="G55" s="17" t="s">
-        <v>258</v>
-      </c>
-      <c r="H55" s="17" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="3">
-        <v>255</v>
-      </c>
-      <c r="B56" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E56" s="7">
-        <v>1.3032183684948084E-2</v>
-      </c>
-      <c r="F56" s="6">
-        <v>10</v>
-      </c>
-      <c r="G56" s="17" t="s">
-        <v>259</v>
-      </c>
-      <c r="H56" s="17" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="3">
-        <v>90</v>
-      </c>
-      <c r="B57" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E57" s="7">
-        <v>1.1808211440281434E-2</v>
-      </c>
-      <c r="F57" s="6">
-        <v>10</v>
-      </c>
-      <c r="G57" s="17" t="s">
-        <v>260</v>
-      </c>
-      <c r="H57" s="17" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="3">
-        <v>153</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E58" s="7">
-        <v>1.1621296174072784E-2</v>
-      </c>
-      <c r="F58" s="6">
-        <v>10</v>
-      </c>
-      <c r="G58" s="17" t="s">
-        <v>261</v>
-      </c>
-      <c r="H58" s="17" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="3">
-        <v>199</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D59" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E59" s="7">
-        <v>1.0391030746663709E-2</v>
-      </c>
-      <c r="F59" s="6">
-        <v>10</v>
-      </c>
-      <c r="G59" s="17" t="s">
-        <v>262</v>
-      </c>
-      <c r="H59" s="17" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="3">
-        <v>47</v>
-      </c>
-      <c r="B60" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E60" s="10">
-        <v>9.2103343959954471E-3</v>
-      </c>
-      <c r="F60" s="6">
-        <v>10</v>
-      </c>
-      <c r="G60" s="17" t="s">
-        <v>263</v>
-      </c>
-      <c r="H60" s="17" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="3">
-        <v>58</v>
-      </c>
-      <c r="B61" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E61" s="10">
-        <v>8.4847454642151248E-3</v>
-      </c>
-      <c r="F61" s="6">
-        <v>9</v>
-      </c>
-      <c r="G61" s="17" t="s">
-        <v>264</v>
-      </c>
-      <c r="H61" s="17" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="3">
-        <v>651</v>
-      </c>
-      <c r="B62" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E62" s="10">
-        <v>8.357851542356241E-3</v>
-      </c>
-      <c r="F62" s="6">
-        <v>10</v>
-      </c>
-      <c r="G62" s="17" t="s">
-        <v>265</v>
-      </c>
-      <c r="H62" s="17" t="s">
+      <c r="F109" s="10">
+        <v>1.7115860121715138E-3</v>
+      </c>
+      <c r="G109" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="H109" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="I109" s="6">
+        <v>1</v>
+      </c>
+      <c r="J109" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="K109" s="18" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="3">
-        <v>665</v>
-      </c>
-      <c r="B63" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E63" s="7">
-        <v>7.9611433347388412E-3</v>
-      </c>
-      <c r="F63" s="6">
-        <v>10</v>
-      </c>
-      <c r="G63" s="17" t="s">
-        <v>266</v>
-      </c>
-      <c r="H63" s="17" t="s">
+      <c r="L109" s="18" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="3">
-        <v>723</v>
-      </c>
-      <c r="B64" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E64" s="10">
-        <v>6.003833613320503E-3</v>
-      </c>
-      <c r="F64" s="6">
-        <v>7</v>
-      </c>
-      <c r="G64" s="17" t="s">
-        <v>267</v>
-      </c>
-      <c r="H64" s="17" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="3">
-        <v>86</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E65" s="10">
-        <v>5.2416647144758709E-3</v>
-      </c>
-      <c r="F65" s="6">
-        <v>1</v>
-      </c>
-      <c r="G65" s="17" t="s">
-        <v>268</v>
-      </c>
-      <c r="H65" s="17" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="3">
-        <v>663</v>
-      </c>
-      <c r="B66" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E66" s="10">
-        <v>4.6460817791641618E-3</v>
-      </c>
-      <c r="F66" s="6">
-        <v>3</v>
-      </c>
-      <c r="G66" s="17">
-        <v>22.8883219475366</v>
-      </c>
-      <c r="H66" s="17">
-        <v>-109.909089347432</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="3">
-        <v>69</v>
-      </c>
-      <c r="B67" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E67" s="10">
-        <v>3.7817545239335749E-3</v>
-      </c>
-      <c r="F67" s="6">
-        <v>4</v>
-      </c>
-      <c r="G67" s="17">
-        <v>19.524310820975899</v>
-      </c>
-      <c r="H67" s="17">
-        <v>-99.212605161489904</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="3">
-        <v>251</v>
-      </c>
-      <c r="B68" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E68" s="7">
-        <v>9.9398063169533236E-3</v>
-      </c>
-      <c r="F68" s="6">
-        <v>10</v>
-      </c>
-      <c r="G68" s="17">
-        <v>20.856669077227899</v>
-      </c>
-      <c r="H68" s="17">
-        <v>-86.898316759161204</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="3">
-        <v>24</v>
-      </c>
-      <c r="B69" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D69" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E69" s="7">
-        <v>1.6640500941968742E-2</v>
-      </c>
-      <c r="F69" s="6">
-        <v>10</v>
-      </c>
-      <c r="G69" s="17">
-        <v>19.368784017256999</v>
-      </c>
-      <c r="H69" s="17">
-        <v>-99.258279196420403</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="3">
-        <v>322</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E70" s="7">
-        <v>1.2340350340891489E-2</v>
-      </c>
-      <c r="F70" s="6">
-        <v>8</v>
-      </c>
-      <c r="G70" s="17">
-        <v>19.436225375766501</v>
-      </c>
-      <c r="H70" s="17">
-        <v>-99.231146598705294</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="3">
-        <v>812</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D71" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E71" s="7">
-        <v>1.1033720708268059E-2</v>
-      </c>
-      <c r="F71" s="6">
-        <v>10</v>
-      </c>
-      <c r="G71" s="17">
-        <v>24.150198891289801</v>
-      </c>
-      <c r="H71" s="17">
-        <v>-110.30713727471399</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="3">
-        <v>789</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D72" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="E72" s="7">
-        <v>2.2300002624919185E-2</v>
-      </c>
-      <c r="F72" s="6">
-        <v>10</v>
-      </c>
-      <c r="G72" s="17">
-        <v>18.520357917287601</v>
-      </c>
-      <c r="H72" s="17">
-        <v>-88.320489356069402</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="3">
-        <v>59</v>
-      </c>
-      <c r="B73" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E73" s="7">
-        <v>1.7395490781259557E-2</v>
-      </c>
-      <c r="F73" s="6">
-        <v>10</v>
-      </c>
-      <c r="G73" s="17">
-        <v>19.5069395561292</v>
-      </c>
-      <c r="H73" s="17">
-        <v>-96.856901032893603</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="3">
-        <v>821</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E74" s="7">
-        <v>9.3069760799181535E-3</v>
-      </c>
-      <c r="F74" s="6">
-        <v>5</v>
-      </c>
-      <c r="G74" s="17">
-        <v>24.139611111582798</v>
-      </c>
-      <c r="H74" s="17">
-        <v>-110.311446023524</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="3">
-        <v>139</v>
-      </c>
-      <c r="B75" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D75" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="E75" s="10">
-        <v>6.7852963838663195E-3</v>
-      </c>
-      <c r="F75" s="6">
-        <v>9</v>
-      </c>
-      <c r="G75" s="17">
-        <v>19.404291781485401</v>
-      </c>
-      <c r="H75" s="17">
-        <v>-99.281308967428501</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="3">
-        <v>270</v>
-      </c>
-      <c r="B76" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D76" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="E76" s="10">
-        <v>3.76686701981193E-3</v>
-      </c>
-      <c r="F76" s="6">
-        <v>4</v>
-      </c>
-      <c r="G76" s="17">
-        <v>19.393101364448601</v>
-      </c>
-      <c r="H76" s="17">
-        <v>99.281880810429598</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="3">
-        <v>78</v>
-      </c>
-      <c r="B77" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C77" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D77" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="E77" s="7">
-        <v>2.8127862242819213E-2</v>
-      </c>
-      <c r="F77" s="6">
-        <v>10</v>
-      </c>
-      <c r="G77" s="17">
-        <v>19.3472672701837</v>
-      </c>
-      <c r="H77" s="17">
-        <v>-99.188014241216393</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="3">
-        <v>253</v>
-      </c>
-      <c r="B78" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E78" s="7">
-        <v>2.1636851085154972E-2</v>
-      </c>
-      <c r="F78" s="6">
-        <v>10</v>
-      </c>
-      <c r="G78" s="17">
-        <v>19.422744140357601</v>
-      </c>
-      <c r="H78" s="17">
-        <v>-99.232715606912905</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="3">
-        <v>281</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C79" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D79" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="E79" s="7">
-        <v>1.7871180555153451E-2</v>
-      </c>
-      <c r="F79" s="6">
-        <v>7</v>
-      </c>
-      <c r="G79" s="17">
-        <v>24.158481541547602</v>
-      </c>
-      <c r="H79" s="17">
-        <v>-110.31101700111699</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="3">
-        <v>135</v>
-      </c>
-      <c r="B80" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E80" s="7">
-        <v>1.1572256224504493E-2</v>
-      </c>
-      <c r="F80" s="6">
-        <v>8</v>
-      </c>
-      <c r="G80" s="17">
-        <v>19.427975833136198</v>
-      </c>
-      <c r="H80" s="17">
-        <v>-99.210460297893604</v>
+    <row r="1048576" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M1048576" s="16" t="s">
+        <v>305</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F80" xr:uid="{3A16AC06-11F1-411E-BC54-C20D4B63FCD4}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="02650 SUPER CHEDRAUI SELECTO INTERLOMAS HILLS 08-19"/>
-        <filter val="28658 SUPERCITO SELECTO LOMAS DE TECAMACHALCO 11-24"/>
-        <filter val="30001 SUPERCITO SELECTO LOMAS COUNTRY 08-22"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:F80">
-      <sortCondition ref="D2:D80"/>
+  <autoFilter ref="A1:I79" xr:uid="{3A16AC06-11F1-411E-BC54-C20D4B63FCD4}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I79">
+      <sortCondition ref="E1:E79"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="E3:E13 E15:E16 E18:E19 E21:E22 E24:E34 E36:E80">
-    <cfRule type="colorScale" priority="36">
+  <conditionalFormatting sqref="F80:H109">
+    <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3801,8 +6771,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:E80">
-    <cfRule type="colorScale" priority="43">
+  <conditionalFormatting sqref="F80:H109">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3813,8 +6783,159 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H19">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G26">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H26">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G34:G35">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H34">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H35">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:H12 F14:H15 F17 F18:H18 F20:H21 F23:H33 F35:H63 F64 H64 F65:H79">
+    <cfRule type="colorScale" priority="57">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:H63 F64 H64 F65:H79">
+    <cfRule type="colorScale" priority="67">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="J80" r:id="rId1" xr:uid="{BFB0E96C-9433-49D0-9823-8AE87F6FEFC4}"/>
+    <hyperlink ref="J81" r:id="rId2" xr:uid="{2C470E57-8396-4E91-9909-D8A7F8DD1714}"/>
+    <hyperlink ref="J82" r:id="rId3" xr:uid="{2E04AEAC-387A-44CC-A704-942106A3DBD9}"/>
+    <hyperlink ref="J83" r:id="rId4" xr:uid="{7D1A45E8-AFF3-4E5C-8F0B-4B66C73BC080}"/>
+    <hyperlink ref="J84" r:id="rId5" xr:uid="{1C3DB39A-8608-483B-B003-EC7E1314D19A}"/>
+    <hyperlink ref="J85" r:id="rId6" xr:uid="{0390FBF9-D570-4187-A9F9-C9EBB7ECA821}"/>
+    <hyperlink ref="J86" r:id="rId7" xr:uid="{48A6022C-B0E0-4E9D-92CA-189684F5B8F2}"/>
+    <hyperlink ref="J87" r:id="rId8" xr:uid="{EE2E6721-C2B5-4CEB-BA5B-1DC57C41E9A8}"/>
+    <hyperlink ref="J88" r:id="rId9" xr:uid="{08F4963A-24A4-4DB8-B254-5E9215ADF32A}"/>
+    <hyperlink ref="J89" r:id="rId10" xr:uid="{A48C0400-4A73-418C-A52A-87E4FAEEC0C3}"/>
+    <hyperlink ref="J90" r:id="rId11" xr:uid="{9A6C29F5-1FCF-4E92-8844-823315D85460}"/>
+    <hyperlink ref="J91" r:id="rId12" xr:uid="{BEC74380-1464-492E-A200-913B201B4FA4}"/>
+    <hyperlink ref="J92" r:id="rId13" xr:uid="{C088CF44-F886-4F24-AE98-7C42CE5CD1AE}"/>
+    <hyperlink ref="J93" r:id="rId14" xr:uid="{22FBA0CD-751F-4474-BF9F-46F274291B4F}"/>
+    <hyperlink ref="J94" r:id="rId15" xr:uid="{4F0641A7-C3AC-4660-82D6-C19E5578386C}"/>
+    <hyperlink ref="J95" r:id="rId16" xr:uid="{D62C9C0C-6DAD-402C-A3E1-00DB3CEF988C}"/>
+    <hyperlink ref="J96" r:id="rId17" xr:uid="{ED66331C-0500-4017-A0D3-C193FB5217B0}"/>
+    <hyperlink ref="J97" r:id="rId18" xr:uid="{0CBF494B-6749-444F-97E1-B4F423C8C25B}"/>
+    <hyperlink ref="J98" r:id="rId19" xr:uid="{CFB021B1-0115-4983-80A7-1C7A30955A9B}"/>
+    <hyperlink ref="J99" r:id="rId20" xr:uid="{8E363670-CB66-47D0-BFD5-7BCE7CA91081}"/>
+    <hyperlink ref="J100" r:id="rId21" xr:uid="{B685A20F-D7BB-405A-B933-448236BF0F66}"/>
+    <hyperlink ref="J101" r:id="rId22" xr:uid="{27096C34-FEF2-479A-B9A3-FAE5674674D9}"/>
+    <hyperlink ref="J102" r:id="rId23" xr:uid="{93C1CF06-3C6B-44FB-BDF1-D7BC6764698C}"/>
+    <hyperlink ref="J103" r:id="rId24" xr:uid="{2A277438-85C0-4FDC-898C-E0E6E015D995}"/>
+    <hyperlink ref="J104" r:id="rId25" xr:uid="{C9A82065-748A-4501-8181-3939A86783CB}"/>
+    <hyperlink ref="J105" r:id="rId26" xr:uid="{9C642B99-623B-4298-8DF0-9A5F71A21F8C}"/>
+    <hyperlink ref="J106" r:id="rId27" xr:uid="{C44D01C8-BCD9-4402-A05E-EF537A125E5E}"/>
+    <hyperlink ref="J107" r:id="rId28" xr:uid="{BD70D72E-34EB-402F-9DF1-A3698FB4C0F9}"/>
+    <hyperlink ref="J108" r:id="rId29" xr:uid="{D5175E39-304B-4CF0-9406-4442A52E11A8}"/>
+    <hyperlink ref="J109" r:id="rId30" xr:uid="{0D195B5E-ABD3-4193-A5E4-91E5D5E94F3B}"/>
+    <hyperlink ref="J12" r:id="rId31" xr:uid="{88A5BF55-463B-4348-99EF-268DD4335945}"/>
+    <hyperlink ref="J11" r:id="rId32" xr:uid="{DD227CB4-E50E-4E14-812A-B3330B8646A3}"/>
+    <hyperlink ref="J13" r:id="rId33" xr:uid="{CE3569CA-76DF-4F9D-A264-4120B8B9397B}"/>
+    <hyperlink ref="J14" r:id="rId34" xr:uid="{F4808826-581E-4C5C-8603-8F5FF306BF8D}"/>
+    <hyperlink ref="J15" r:id="rId35" xr:uid="{32D60BB1-593A-4608-8E98-012133A3BBCF}"/>
+    <hyperlink ref="J16" r:id="rId36" xr:uid="{4FC73B8D-D981-404B-A437-2D2D969AB25E}"/>
+    <hyperlink ref="J17" r:id="rId37" xr:uid="{017F71BF-D145-4C59-AE50-3C20CFEC4F4F}"/>
+    <hyperlink ref="J18" r:id="rId38" xr:uid="{7630FD17-D0A7-45EA-83BD-9C38CC2A9B41}"/>
+    <hyperlink ref="J19" r:id="rId39" xr:uid="{E8908A6E-9D09-45CD-B809-26E40ED23C7B}"/>
+    <hyperlink ref="J20" r:id="rId40" xr:uid="{CFA7C5A1-E280-4098-8DEA-A826A1DBBD8D}"/>
+    <hyperlink ref="J43" r:id="rId41" xr:uid="{3F69C7F5-A773-4647-B0DF-39142BA30056}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId42"/>
 </worksheet>
 </file>
 
@@ -3857,10 +6978,10 @@
         <v>162</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>300</v>
+        <v>215</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>301</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -3886,10 +7007,10 @@
         <v>163</v>
       </c>
       <c r="H3" t="s">
-        <v>302</v>
+        <v>217</v>
       </c>
       <c r="I3" t="s">
-        <v>303</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -3915,10 +7036,10 @@
         <v>164</v>
       </c>
       <c r="H4" t="s">
-        <v>304</v>
+        <v>219</v>
       </c>
       <c r="I4" t="s">
-        <v>305</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -3944,10 +7065,10 @@
         <v>165</v>
       </c>
       <c r="H5" t="s">
-        <v>306</v>
+        <v>221</v>
       </c>
       <c r="I5" t="s">
-        <v>307</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -3973,10 +7094,10 @@
         <v>166</v>
       </c>
       <c r="H6" t="s">
-        <v>308</v>
+        <v>223</v>
       </c>
       <c r="I6" t="s">
-        <v>309</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -4002,10 +7123,10 @@
         <v>167</v>
       </c>
       <c r="H7" t="s">
-        <v>310</v>
+        <v>225</v>
       </c>
       <c r="I7" t="s">
-        <v>311</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -4031,10 +7152,10 @@
         <v>168</v>
       </c>
       <c r="H8" t="s">
-        <v>312</v>
+        <v>227</v>
       </c>
       <c r="I8" t="s">
-        <v>313</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -4060,10 +7181,10 @@
         <v>169</v>
       </c>
       <c r="H9" t="s">
-        <v>314</v>
+        <v>229</v>
       </c>
       <c r="I9" t="s">
-        <v>315</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -4089,10 +7210,10 @@
         <v>170</v>
       </c>
       <c r="H10" t="s">
-        <v>316</v>
+        <v>231</v>
       </c>
       <c r="I10" t="s">
-        <v>317</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -4118,10 +7239,10 @@
         <v>171</v>
       </c>
       <c r="H11" t="s">
-        <v>318</v>
+        <v>233</v>
       </c>
       <c r="I11" t="s">
-        <v>319</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -4147,10 +7268,10 @@
         <v>172</v>
       </c>
       <c r="H12" t="s">
-        <v>320</v>
+        <v>235</v>
       </c>
       <c r="I12" t="s">
-        <v>321</v>
+        <v>236</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -4176,10 +7297,10 @@
         <v>173</v>
       </c>
       <c r="H13" t="s">
-        <v>322</v>
+        <v>237</v>
       </c>
       <c r="I13" t="s">
-        <v>323</v>
+        <v>238</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -4205,10 +7326,10 @@
         <v>174</v>
       </c>
       <c r="H14" t="s">
-        <v>324</v>
+        <v>239</v>
       </c>
       <c r="I14" t="s">
-        <v>325</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -4234,10 +7355,10 @@
         <v>175</v>
       </c>
       <c r="H15" t="s">
-        <v>326</v>
+        <v>241</v>
       </c>
       <c r="I15" t="s">
-        <v>327</v>
+        <v>242</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -4263,10 +7384,10 @@
         <v>176</v>
       </c>
       <c r="H16" t="s">
-        <v>328</v>
+        <v>243</v>
       </c>
       <c r="I16" t="s">
-        <v>329</v>
+        <v>244</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -4292,10 +7413,10 @@
         <v>177</v>
       </c>
       <c r="H17" t="s">
-        <v>330</v>
+        <v>245</v>
       </c>
       <c r="I17" t="s">
-        <v>331</v>
+        <v>246</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -4321,10 +7442,10 @@
         <v>178</v>
       </c>
       <c r="H18" t="s">
-        <v>332</v>
+        <v>247</v>
       </c>
       <c r="I18" t="s">
-        <v>333</v>
+        <v>248</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -4350,10 +7471,10 @@
         <v>179</v>
       </c>
       <c r="H19" t="s">
-        <v>334</v>
+        <v>249</v>
       </c>
       <c r="I19" t="s">
-        <v>335</v>
+        <v>250</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -4379,10 +7500,10 @@
         <v>180</v>
       </c>
       <c r="H20" t="s">
-        <v>336</v>
+        <v>251</v>
       </c>
       <c r="I20" t="s">
-        <v>337</v>
+        <v>252</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -4408,10 +7529,10 @@
         <v>181</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>338</v>
+        <v>253</v>
       </c>
       <c r="I21" s="18" t="s">
-        <v>339</v>
+        <v>254</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -4440,7 +7561,7 @@
         <v>19.548992839452801</v>
       </c>
       <c r="I22" s="18" t="s">
-        <v>340</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -4466,10 +7587,10 @@
         <v>183</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>341</v>
+        <v>256</v>
       </c>
       <c r="I23" s="18" t="s">
-        <v>342</v>
+        <v>257</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -4495,10 +7616,10 @@
         <v>184</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>343</v>
+        <v>258</v>
       </c>
       <c r="I24" s="18" t="s">
-        <v>344</v>
+        <v>259</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -4527,7 +7648,7 @@
         <v>22.129746078133198</v>
       </c>
       <c r="I25" s="18" t="s">
-        <v>345</v>
+        <v>260</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -4556,7 +7677,7 @@
         <v>19.506940269783399</v>
       </c>
       <c r="I26" s="18" t="s">
-        <v>346</v>
+        <v>261</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -4582,10 +7703,10 @@
         <v>187</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>347</v>
+        <v>262</v>
       </c>
       <c r="I27" s="18" t="s">
-        <v>348</v>
+        <v>263</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -4611,10 +7732,10 @@
         <v>188</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>349</v>
+        <v>264</v>
       </c>
       <c r="I28" s="18" t="s">
-        <v>350</v>
+        <v>265</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -4640,10 +7761,10 @@
         <v>189</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>351</v>
+        <v>266</v>
       </c>
       <c r="I29" s="18" t="s">
-        <v>352</v>
+        <v>267</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -4669,7 +7790,7 @@
         <v>190</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>353</v>
+        <v>268</v>
       </c>
       <c r="I30" s="18">
         <v>-99.179037170726104</v>
@@ -4698,10 +7819,10 @@
         <v>191</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>354</v>
+        <v>269</v>
       </c>
       <c r="I31" s="18" t="s">
-        <v>355</v>
+        <v>270</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -4727,10 +7848,10 @@
         <v>192</v>
       </c>
       <c r="H32" s="18" t="s">
-        <v>356</v>
+        <v>271</v>
       </c>
       <c r="I32" s="18" t="s">
-        <v>357</v>
+        <v>272</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -4756,10 +7877,10 @@
         <v>193</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>358</v>
+        <v>273</v>
       </c>
       <c r="I33" s="18" t="s">
-        <v>359</v>
+        <v>274</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -4788,7 +7909,7 @@
         <v>23.0440959197166</v>
       </c>
       <c r="I34" s="18" t="s">
-        <v>360</v>
+        <v>275</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -4817,7 +7938,7 @@
         <v>19.272015139846602</v>
       </c>
       <c r="I35" s="18" t="s">
-        <v>361</v>
+        <v>276</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -4875,7 +7996,7 @@
         <v>20.897403003383801</v>
       </c>
       <c r="I37" s="18" t="s">
-        <v>362</v>
+        <v>277</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -4901,10 +8022,10 @@
         <v>198</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>363</v>
+        <v>278</v>
       </c>
       <c r="I38" s="18" t="s">
-        <v>364</v>
+        <v>279</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -4930,10 +8051,10 @@
         <v>199</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>365</v>
+        <v>280</v>
       </c>
       <c r="I39" s="18" t="s">
-        <v>366</v>
+        <v>281</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -4962,7 +8083,7 @@
         <v>19.3884836634716</v>
       </c>
       <c r="I40" s="18" t="s">
-        <v>367</v>
+        <v>282</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -4988,10 +8109,10 @@
         <v>201</v>
       </c>
       <c r="H41" s="18" t="s">
-        <v>368</v>
+        <v>283</v>
       </c>
       <c r="I41" s="18" t="s">
-        <v>369</v>
+        <v>284</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -5017,10 +8138,10 @@
         <v>202</v>
       </c>
       <c r="H42" s="18" t="s">
-        <v>370</v>
+        <v>285</v>
       </c>
       <c r="I42" s="18" t="s">
-        <v>371</v>
+        <v>286</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -5049,7 +8170,7 @@
         <v>20.6076550152689</v>
       </c>
       <c r="I43" s="18" t="s">
-        <v>372</v>
+        <v>287</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -5078,7 +8199,7 @@
         <v>19.417376983685099</v>
       </c>
       <c r="I44" s="18" t="s">
-        <v>373</v>
+        <v>288</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -5104,10 +8225,10 @@
         <v>205</v>
       </c>
       <c r="H45" s="18" t="s">
-        <v>374</v>
+        <v>289</v>
       </c>
       <c r="I45" s="18" t="s">
-        <v>375</v>
+        <v>290</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -5136,7 +8257,7 @@
         <v>20.643285180687901</v>
       </c>
       <c r="I46" s="18" t="s">
-        <v>376</v>
+        <v>291</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -5165,7 +8286,7 @@
         <v>19.3827979499045</v>
       </c>
       <c r="I47" s="18" t="s">
-        <v>377</v>
+        <v>292</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -5191,10 +8312,10 @@
         <v>208</v>
       </c>
       <c r="H48" s="18" t="s">
-        <v>378</v>
+        <v>293</v>
       </c>
       <c r="I48" s="18" t="s">
-        <v>379</v>
+        <v>294</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -5223,7 +8344,7 @@
         <v>19.165077004486399</v>
       </c>
       <c r="I49" s="18" t="s">
-        <v>380</v>
+        <v>295</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -5249,16 +8370,16 @@
         <v>210</v>
       </c>
       <c r="H50" s="18" t="s">
-        <v>381</v>
+        <v>296</v>
       </c>
       <c r="I50" s="18" t="s">
-        <v>382</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:F50" xr:uid="{52CE2E43-0DFC-40AA-B05B-C9CB075EA9CC}"/>
-  <conditionalFormatting sqref="E3 E5 E7:E10 E12:E15 E17:E50">
-    <cfRule type="colorScale" priority="50">
+  <conditionalFormatting sqref="E3:E50">
+    <cfRule type="colorScale" priority="56">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5269,8 +8390,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:E50">
-    <cfRule type="colorScale" priority="56">
+  <conditionalFormatting sqref="E5 E3 E7:E10 E12:E15 E17:E50">
+    <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/Listado de Tiendas_Augusto.xlsx
+++ b/Listado de Tiendas_Augusto.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Desarrollos\u_\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\desarrollo\Euro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1923D4D-F160-47EE-A206-668458435CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C280C46B-C2B3-4860-A0D6-1A6956B04567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{4944A775-6BF1-43BB-880A-09CB389DE030}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4944A775-6BF1-43BB-880A-09CB389DE030}"/>
   </bookViews>
   <sheets>
     <sheet name="CHEDRAUI" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="590">
   <si>
     <t>Tienda</t>
   </si>
@@ -676,15 +676,9 @@
     <t>https://maps.app.goo.gl/YqEtAY5gpfYk1G8b8</t>
   </si>
   <si>
-    <t>19.310666760356014</t>
-  </si>
-  <si>
     <t>24.165825561511703</t>
   </si>
   <si>
-    <t>-99.63525232219332</t>
-  </si>
-  <si>
     <t>110.31221644427187</t>
   </si>
   <si>
@@ -1790,6 +1784,33 @@
   </si>
   <si>
     <t>Valle de Bravo</t>
+  </si>
+  <si>
+    <t>-100.39712058465837</t>
+  </si>
+  <si>
+    <t>20.54681278891245</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/zP9uHT9gauoSRfqv8</t>
+  </si>
+  <si>
+    <t>Ciudad López Mateos</t>
+  </si>
+  <si>
+    <t>Tulúm</t>
+  </si>
+  <si>
+    <t>Ciudad Satélite</t>
+  </si>
+  <si>
+    <t>Corregidora</t>
+  </si>
+  <si>
+    <t>La Paz</t>
+  </si>
+  <si>
+    <t>Tuxtla Gutiérrez</t>
   </si>
 </sst>
 </file>
@@ -1955,7 +1976,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2013,7 +2034,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
@@ -2038,11 +2059,30 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2362,7 +2402,7 @@
   <dimension ref="A1:N1048576"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.42578125" style="38" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="66" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.140625" bestFit="1" customWidth="1"/>
@@ -2377,14 +2417,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -2396,10 +2436,10 @@
         <v>3</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>4</v>
@@ -2408,10 +2448,10 @@
         <v>162</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="M1" s="13" t="s">
         <v>88</v>
@@ -2420,523 +2460,559 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
-        <v>196</v>
+        <v>13</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F2" s="7">
-        <v>1.3838290082880884E-2</v>
-      </c>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
+        <v>1.12892803485364E-2</v>
+      </c>
+      <c r="G2" s="34" t="s">
+        <v>589</v>
+      </c>
+      <c r="H2" s="34" t="s">
+        <v>589</v>
+      </c>
       <c r="I2" s="6">
         <v>10</v>
       </c>
-      <c r="J2" s="21" t="s">
-        <v>306</v>
+      <c r="J2" s="32" t="s">
+        <v>304</v>
       </c>
       <c r="K2" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="L2" s="17" t="s">
+        <v>302</v>
+      </c>
+      <c r="M2" s="16" t="s">
         <v>303</v>
-      </c>
-      <c r="L2" s="17" t="s">
-        <v>304</v>
-      </c>
-      <c r="M2" s="16" t="s">
-        <v>305</v>
       </c>
       <c r="N2" s="16"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>127</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F3" s="7">
-        <v>2.159342568746472E-2</v>
-      </c>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
+        <v>14</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F3" s="10">
+        <v>3.8276328024454062E-3</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>386</v>
+      </c>
       <c r="I3" s="6">
-        <v>10</v>
-      </c>
-      <c r="J3" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="32" t="s">
+        <v>305</v>
+      </c>
+      <c r="K3" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="L3" s="17" t="s">
         <v>307</v>
       </c>
-      <c r="K3" s="17" t="s">
-        <v>308</v>
-      </c>
-      <c r="L3" s="17" t="s">
-        <v>309</v>
-      </c>
       <c r="M3" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N3" s="16"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>333</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>61</v>
+        <v>24</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F4" s="10">
-        <v>7.8252122337391823E-3</v>
-      </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
+        <v>98</v>
+      </c>
+      <c r="F4" s="7">
+        <v>1.6640500941968742E-2</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>441</v>
+      </c>
       <c r="I4" s="6">
-        <v>5</v>
-      </c>
-      <c r="J4" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="32" t="s">
+        <v>308</v>
+      </c>
+      <c r="K4" s="17" t="s">
         <v>310</v>
       </c>
-      <c r="K4" s="17" t="s">
-        <v>312</v>
-      </c>
       <c r="L4" s="17" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="M4" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N4" s="16"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>178</v>
+        <v>47</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F5" s="10">
-        <v>6.0846674247843667E-3</v>
-      </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
+        <v>9.2103343959954471E-3</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>490</v>
+      </c>
       <c r="I5" s="6">
         <v>10</v>
       </c>
-      <c r="J5" s="21" t="s">
+      <c r="J5" s="32" t="s">
+        <v>311</v>
+      </c>
+      <c r="K5" s="17" t="s">
         <v>313</v>
       </c>
-      <c r="K5" s="17" t="s">
-        <v>315</v>
-      </c>
       <c r="L5" s="17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M5" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N5" s="16"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>802</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>73</v>
+        <v>52</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F6" s="10">
-        <v>5.0952928104922666E-3</v>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
+        <v>102</v>
+      </c>
+      <c r="F6" s="7">
+        <v>9.6955214810818292E-3</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>475</v>
+      </c>
       <c r="I6" s="6">
         <v>10</v>
       </c>
-      <c r="J6" s="21" t="s">
+      <c r="J6" s="32" t="s">
+        <v>314</v>
+      </c>
+      <c r="K6" s="17" t="s">
         <v>316</v>
       </c>
-      <c r="K6" s="17" t="s">
-        <v>318</v>
-      </c>
       <c r="L6" s="17" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="M6" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N6" s="16"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>126</v>
+        <v>58</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F7" s="10">
-        <v>4.2220204530022372E-3</v>
-      </c>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
+        <v>8.4847454642151248E-3</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>428</v>
+      </c>
       <c r="I7" s="6">
-        <v>10</v>
-      </c>
-      <c r="J7" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="32" t="s">
+        <v>317</v>
+      </c>
+      <c r="K7" s="17" t="s">
         <v>319</v>
       </c>
-      <c r="K7" s="17" t="s">
-        <v>321</v>
-      </c>
       <c r="L7" s="17" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N7" s="16"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>330</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>81</v>
+        <v>59</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>27</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F8" s="10">
-        <v>3.7043088476581844E-3</v>
-      </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
+        <v>93</v>
+      </c>
+      <c r="F8" s="7">
+        <v>1.7395490781259557E-2</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>550</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>442</v>
+      </c>
       <c r="I8" s="6">
-        <v>7</v>
-      </c>
-      <c r="J8" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" s="32" t="s">
+        <v>320</v>
+      </c>
+      <c r="K8" s="17" t="s">
         <v>322</v>
       </c>
-      <c r="K8" s="17" t="s">
-        <v>324</v>
-      </c>
       <c r="L8" s="17" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N8" s="16"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>334</v>
+        <v>62</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F9" s="10">
-        <v>1.8709650274066469E-3</v>
-      </c>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
+        <v>89</v>
+      </c>
+      <c r="F9" s="7">
+        <v>1.3994423922537694E-2</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>485</v>
+      </c>
       <c r="I9" s="6">
-        <v>7</v>
-      </c>
-      <c r="J9" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9" s="32" t="s">
+        <v>323</v>
+      </c>
+      <c r="K9" s="17" t="s">
         <v>325</v>
       </c>
-      <c r="K9" s="17" t="s">
-        <v>327</v>
-      </c>
       <c r="L9" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N9" s="16"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="F10" s="7">
-        <v>1.12892803485364E-2</v>
-      </c>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="F10" s="10">
+        <v>3.7817545239335749E-3</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>453</v>
+      </c>
       <c r="I10" s="6">
-        <v>10</v>
-      </c>
-      <c r="J10" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="J10" s="32" t="s">
+        <v>328</v>
+      </c>
+      <c r="K10" s="17" t="s">
         <v>330</v>
       </c>
-      <c r="K10" s="17" t="s">
-        <v>332</v>
-      </c>
       <c r="L10" s="17" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N10" s="16"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>235</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="F11" s="7">
-        <v>3.5985967166643498E-2</v>
+        <v>76</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F11" s="10">
+        <v>1.5680281276461372E-2</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>342</v>
+        <v>386</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>342</v>
+        <v>586</v>
       </c>
       <c r="I11" s="6">
         <v>10</v>
       </c>
       <c r="J11" s="22" t="s">
+        <v>331</v>
+      </c>
+      <c r="K11" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="K11" s="17" t="s">
-        <v>335</v>
-      </c>
       <c r="L11" s="17" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N11" s="16"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>182</v>
+        <v>78</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>6</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F12" s="7">
-        <v>3.5644074373929843E-2</v>
+        <v>2.8127862242819213E-2</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>341</v>
+        <v>564</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>341</v>
+        <v>564</v>
       </c>
       <c r="I12" s="6">
         <v>10</v>
       </c>
       <c r="J12" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="K12" s="17" t="s">
         <v>336</v>
       </c>
-      <c r="K12" s="17" t="s">
-        <v>338</v>
-      </c>
       <c r="L12" s="17" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N12" s="16"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>174</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>10</v>
+        <v>86</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>71</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F13" s="7">
-        <v>3.0428341835977236E-2</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>340</v>
+        <v>89</v>
+      </c>
+      <c r="F13" s="10">
+        <v>5.2416647144758709E-3</v>
+      </c>
+      <c r="G13" s="35" t="s">
+        <v>525</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>457</v>
       </c>
       <c r="I13" s="6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J13" s="22" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="K13" s="17" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L13" s="17" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N13" s="16"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F14" s="7">
-        <v>2.8799763282912907E-2</v>
+        <v>1.1808211440281434E-2</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>348</v>
+        <v>485</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>348</v>
+        <v>485</v>
       </c>
       <c r="I14" s="6">
         <v>10</v>
       </c>
       <c r="J14" s="22" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="L14" s="17" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N14" s="16"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>232</v>
+        <v>98</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>8</v>
@@ -2945,1414 +3021,1414 @@
         <v>90</v>
       </c>
       <c r="F15" s="7">
-        <v>2.8733897314624928E-2</v>
+        <v>2.8799763282912907E-2</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="I15" s="6">
         <v>10</v>
       </c>
       <c r="J15" s="22" t="s">
+        <v>347</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>350</v>
+      </c>
+      <c r="L15" s="17" t="s">
         <v>349</v>
       </c>
-      <c r="K15" s="17" t="s">
-        <v>352</v>
-      </c>
-      <c r="L15" s="17" t="s">
-        <v>351</v>
-      </c>
       <c r="M15" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N15" s="16"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>233</v>
+        <v>99</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F16" s="7">
-        <v>2.1515404807174253E-2</v>
+        <v>2.1965990704229194E-2</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>354</v>
+        <v>433</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>354</v>
+        <v>433</v>
       </c>
       <c r="I16" s="6">
         <v>10</v>
       </c>
       <c r="J16" s="22" t="s">
+        <v>351</v>
+      </c>
+      <c r="K16" s="23" t="s">
+        <v>354</v>
+      </c>
+      <c r="L16" s="23" t="s">
         <v>353</v>
       </c>
-      <c r="K16" s="23" t="s">
-        <v>356</v>
-      </c>
-      <c r="L16" s="23" t="s">
-        <v>355</v>
-      </c>
       <c r="M16" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N16" s="16"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <v>177</v>
+        <v>106</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F17" s="7">
-        <v>2.0063778202674572E-2</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>354</v>
+        <v>1.4224459723031085E-2</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>386</v>
       </c>
       <c r="I17" s="6">
         <v>10</v>
       </c>
       <c r="J17" s="22" t="s">
+        <v>355</v>
+      </c>
+      <c r="K17" s="17" t="s">
         <v>357</v>
       </c>
-      <c r="K17" s="17" t="s">
-        <v>359</v>
-      </c>
       <c r="L17" s="17" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="N17" s="16"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
-        <v>814</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>90</v>
+        <v>107</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>161</v>
       </c>
       <c r="F18" s="7">
-        <v>1.1317007292279867E-2</v>
+        <v>1.4652280469027492E-2</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>342</v>
+        <v>522</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>342</v>
+        <v>522</v>
       </c>
       <c r="I18" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J18" s="22" t="s">
+        <v>358</v>
+      </c>
+      <c r="K18" s="17" t="s">
         <v>360</v>
       </c>
-      <c r="K18" s="17" t="s">
-        <v>362</v>
-      </c>
       <c r="L18" s="17" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N18" s="16"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <v>587</v>
+        <v>108</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F19" s="10">
-        <v>9.8573962791872784E-3</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>350</v>
+        <v>7.5133013260082855E-3</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>449</v>
       </c>
       <c r="I19" s="6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J19" s="22" t="s">
+        <v>362</v>
+      </c>
+      <c r="K19" s="17" t="s">
+        <v>363</v>
+      </c>
+      <c r="L19" s="17" t="s">
         <v>364</v>
       </c>
-      <c r="K19" s="17" t="s">
-        <v>365</v>
-      </c>
-      <c r="L19" s="17" t="s">
-        <v>366</v>
-      </c>
       <c r="M19" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N19" s="16"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <v>819</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>65</v>
+        <v>109</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F20" s="10">
-        <v>6.4709636133180506E-3</v>
+        <v>2.8137215642739595E-3</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="I20" s="6">
         <v>5</v>
       </c>
       <c r="J20" s="22" t="s">
+        <v>365</v>
+      </c>
+      <c r="K20" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="L20" s="17" t="s">
         <v>367</v>
       </c>
-      <c r="K20" s="17" t="s">
-        <v>370</v>
-      </c>
-      <c r="L20" s="17" t="s">
-        <v>369</v>
-      </c>
       <c r="M20" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N20" s="16"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <v>890</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>68</v>
+        <v>126</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F21" s="10">
-        <v>5.9978222327954078E-3</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>368</v>
+        <v>4.2220204530022372E-3</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>588</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>588</v>
       </c>
       <c r="I21" s="6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J21" s="21" t="s">
+        <v>369</v>
+      </c>
+      <c r="K21" s="17" t="s">
         <v>371</v>
       </c>
-      <c r="K21" s="17" t="s">
-        <v>373</v>
-      </c>
       <c r="L21" s="17" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N21" s="16"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <v>234</v>
+        <v>127</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="F22" s="10">
-        <v>5.5039431087518598E-3</v>
-      </c>
-      <c r="G22" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22" s="7">
+        <v>2.159342568746472E-2</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>588</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>588</v>
+      </c>
+      <c r="I22" s="6">
+        <v>10</v>
+      </c>
+      <c r="J22" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="K22" s="17" t="s">
         <v>375</v>
       </c>
-      <c r="H22" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="I22" s="6">
-        <v>5</v>
-      </c>
-      <c r="J22" s="21" t="s">
+      <c r="L22" s="17" t="s">
         <v>374</v>
       </c>
-      <c r="K22" s="17" t="s">
-        <v>377</v>
-      </c>
-      <c r="L22" s="17" t="s">
-        <v>376</v>
-      </c>
       <c r="M22" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N22" s="16"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <v>652</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E23" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E23" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="F23" s="10">
-        <v>4.4700385807039094E-3</v>
-      </c>
-      <c r="G23" s="10" t="s">
+      <c r="F23" s="7">
+        <v>2.1213529829138978E-2</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="I23" s="6">
+        <v>10</v>
+      </c>
+      <c r="J23" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="K23" s="17" t="s">
         <v>379</v>
       </c>
-      <c r="H23" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="I23" s="6">
-        <v>8</v>
-      </c>
-      <c r="J23" s="21" t="s">
+      <c r="L23" s="17" t="s">
         <v>378</v>
       </c>
-      <c r="K23" s="17" t="s">
-        <v>381</v>
-      </c>
-      <c r="L23" s="17" t="s">
-        <v>380</v>
-      </c>
       <c r="M23" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N23" s="16"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
-        <v>551</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>84</v>
+        <v>135</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>45</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F24" s="10">
-        <v>2.7839409844576937E-3</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="H24" s="10" t="s">
-        <v>379</v>
+        <v>91</v>
+      </c>
+      <c r="F24" s="7">
+        <v>1.1572256224504493E-2</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>564</v>
       </c>
       <c r="I24" s="6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J24" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="K24" s="17" t="s">
         <v>382</v>
       </c>
-      <c r="K24" s="17" t="s">
-        <v>384</v>
-      </c>
       <c r="L24" s="17" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N24" s="16"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
-        <v>552</v>
+        <v>137</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>100</v>
+        <v>154</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>90</v>
       </c>
       <c r="F25" s="10">
-        <v>2.0431194829814742E-3</v>
+        <v>4.9108683201326657E-3</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>388</v>
+        <v>346</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>389</v>
+        <v>346</v>
       </c>
       <c r="I25" s="6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J25" s="21" t="s">
+        <v>383</v>
+      </c>
+      <c r="K25" s="17" t="s">
         <v>385</v>
       </c>
-      <c r="K25" s="17" t="s">
-        <v>387</v>
-      </c>
       <c r="L25" s="17" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="M25" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N25" s="16"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
-        <v>807</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>87</v>
+        <v>138</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>37</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="F26" s="10">
-        <v>1.7718440648280807E-3</v>
+        <v>103</v>
+      </c>
+      <c r="F26" s="7">
+        <v>1.2742149458657334E-2</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>350</v>
+        <v>432</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>350</v>
+        <v>432</v>
       </c>
       <c r="I26" s="6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J26" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="K26" s="17" t="s">
+        <v>392</v>
+      </c>
+      <c r="L26" s="17" t="s">
         <v>393</v>
       </c>
-      <c r="K26" s="17" t="s">
-        <v>394</v>
-      </c>
-      <c r="L26" s="17" t="s">
-        <v>395</v>
-      </c>
       <c r="M26" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N26" s="16"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F27" s="7">
-        <v>1.4224459723031085E-2</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>388</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>388</v>
+        <v>93</v>
+      </c>
+      <c r="F27" s="10">
+        <v>6.7852963838663195E-3</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>552</v>
       </c>
       <c r="I27" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J27" s="21" t="s">
+        <v>394</v>
+      </c>
+      <c r="K27" s="17" t="s">
         <v>396</v>
       </c>
-      <c r="K27" s="17" t="s">
-        <v>398</v>
-      </c>
       <c r="L27" s="17" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="M27" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N27" s="16"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
-        <v>243</v>
+        <v>153</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F28" s="7">
-        <v>1.2407844110385346E-2</v>
+        <v>1.1621296174072784E-2</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>390</v>
+        <v>427</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>390</v>
+        <v>427</v>
       </c>
       <c r="I28" s="6">
         <v>10</v>
       </c>
       <c r="J28" s="21" t="s">
+        <v>397</v>
+      </c>
+      <c r="K28" s="17" t="s">
         <v>399</v>
       </c>
-      <c r="K28" s="17" t="s">
-        <v>401</v>
-      </c>
       <c r="L28" s="17" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="M28" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N28" s="16"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
-        <v>236</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>100</v>
+        <v>153</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="F29" s="10">
-        <v>8.654823259147992E-3</v>
+        <v>1.2999251960434605E-2</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>405</v>
+        <v>577</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>405</v>
+        <v>577</v>
       </c>
       <c r="I29" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J29" s="21" t="s">
+        <v>400</v>
+      </c>
+      <c r="K29" s="17" t="s">
         <v>402</v>
       </c>
-      <c r="K29" s="17" t="s">
-        <v>404</v>
-      </c>
       <c r="L29" s="17" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="M29" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N29" s="16"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
-        <v>277</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>59</v>
+        <v>174</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>10</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F30" s="10">
-        <v>8.2392928977464593E-3</v>
-      </c>
-      <c r="G30" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="F30" s="7">
+        <v>3.0428341835977236E-2</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="I30" s="6">
+        <v>10</v>
+      </c>
+      <c r="J30" s="21" t="s">
+        <v>405</v>
+      </c>
+      <c r="K30" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="L30" s="17" t="s">
         <v>406</v>
       </c>
-      <c r="H30" s="10" t="s">
-        <v>406</v>
-      </c>
-      <c r="I30" s="6">
-        <v>4</v>
-      </c>
-      <c r="J30" s="21" t="s">
-        <v>407</v>
-      </c>
-      <c r="K30" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="L30" s="17" t="s">
-        <v>408</v>
-      </c>
       <c r="M30" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N30" s="16"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
-        <v>858</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>72</v>
+        <v>177</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>23</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F31" s="10">
-        <v>5.1049684701715108E-3</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>413</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>413</v>
+        <v>90</v>
+      </c>
+      <c r="F31" s="7">
+        <v>2.0063778202674572E-2</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>352</v>
       </c>
       <c r="I31" s="6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J31" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="K31" s="17" t="s">
         <v>410</v>
       </c>
-      <c r="K31" s="17" t="s">
-        <v>412</v>
-      </c>
       <c r="L31" s="17" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="M31" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N31" s="16"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
-        <v>667</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>74</v>
+        <v>178</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>66</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F32" s="10">
-        <v>4.7611312961400119E-3</v>
+        <v>6.0846674247843667E-3</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>405</v>
+        <v>577</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>405</v>
+        <v>577</v>
       </c>
       <c r="I32" s="6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J32" s="21" t="s">
+        <v>412</v>
+      </c>
+      <c r="K32" s="17" t="s">
         <v>414</v>
       </c>
-      <c r="K32" s="17" t="s">
-        <v>416</v>
-      </c>
       <c r="L32" s="17" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="M32" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N32" s="16"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
-        <v>576</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>77</v>
+        <v>182</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>9</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F33" s="10">
-        <v>4.4154705511015406E-3</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>388</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>388</v>
+        <v>90</v>
+      </c>
+      <c r="F33" s="7">
+        <v>3.5644074373929843E-2</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>339</v>
       </c>
       <c r="I33" s="6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J33" s="21" t="s">
+        <v>415</v>
+      </c>
+      <c r="K33" s="17" t="s">
         <v>417</v>
       </c>
-      <c r="K33" s="17" t="s">
-        <v>419</v>
-      </c>
       <c r="L33" s="17" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="M33" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N33" s="16"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
-        <v>808</v>
+        <v>186</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>82</v>
+        <v>24</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F34" s="10">
-        <v>2.8538681137612394E-3</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>388</v>
-      </c>
-      <c r="H34" s="10" t="s">
-        <v>388</v>
+        <v>95</v>
+      </c>
+      <c r="F34" s="7">
+        <v>1.9348457402295335E-2</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="I34" s="6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J34" s="21" t="s">
+        <v>418</v>
+      </c>
+      <c r="K34" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="K34" s="17" t="s">
-        <v>422</v>
-      </c>
       <c r="L34" s="17" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="M34" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N34" s="16"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
-        <v>109</v>
+        <v>196</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F35" s="10">
-        <v>2.8137215642739595E-3</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>388</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>388</v>
+        <v>101</v>
+      </c>
+      <c r="F35" s="7">
+        <v>1.3838290082880884E-2</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>101</v>
       </c>
       <c r="I35" s="6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J35" s="21" t="s">
+        <v>421</v>
+      </c>
+      <c r="K35" s="17" t="s">
+        <v>422</v>
+      </c>
+      <c r="L35" s="17" t="s">
         <v>423</v>
       </c>
-      <c r="K35" s="17" t="s">
-        <v>424</v>
-      </c>
-      <c r="L35" s="17" t="s">
-        <v>425</v>
-      </c>
       <c r="M35" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N35" s="16"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
-        <v>267</v>
+        <v>199</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F36" s="7">
-        <v>1.6868828351766882E-2</v>
+        <v>1.0391030746663709E-2</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>427</v>
+        <v>485</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>427</v>
+        <v>485</v>
       </c>
       <c r="I36" s="6">
         <v>10</v>
       </c>
       <c r="J36" s="21" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="K36" s="17" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="L36" s="17" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="M36" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N36" s="16"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
-        <v>138</v>
+        <v>232</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="F37" s="7">
-        <v>1.2742149458657334E-2</v>
+        <v>2.8733897314624928E-2</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>434</v>
+        <v>348</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>434</v>
+        <v>348</v>
       </c>
       <c r="I37" s="6">
         <v>10</v>
       </c>
       <c r="J37" s="21" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="K37" s="17" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="L37" s="17" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="M37" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N37" s="16"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
-        <v>779</v>
+        <v>233</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="F38" s="7">
-        <v>1.4440810477971976E-2</v>
+        <v>2.1515404807174253E-2</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>439</v>
+        <v>352</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>439</v>
+        <v>352</v>
       </c>
       <c r="I38" s="6">
         <v>10</v>
       </c>
       <c r="J38" s="21" t="s">
+        <v>436</v>
+      </c>
+      <c r="K38" s="17" t="s">
         <v>438</v>
       </c>
-      <c r="K38" s="17" t="s">
-        <v>440</v>
-      </c>
       <c r="L38" s="17" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="M38" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N38" s="16"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
-        <v>262</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>25</v>
+        <v>234</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F39" s="7">
-        <v>1.8838172247292208E-2</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>158</v>
+        <v>90</v>
+      </c>
+      <c r="F39" s="10">
+        <v>5.5039431087518598E-3</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>373</v>
       </c>
       <c r="I39" s="6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J39" s="21" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="K39" s="17" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="L39" s="17" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="M39" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N39" s="16"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="F40" s="7">
-        <v>1.1735425361113359E-2</v>
+        <v>3.5985967166643498E-2</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>158</v>
+        <v>340</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>158</v>
+        <v>340</v>
       </c>
       <c r="I40" s="6">
         <v>10</v>
       </c>
       <c r="J40" s="21" t="s">
+        <v>445</v>
+      </c>
+      <c r="K40" s="17" t="s">
         <v>447</v>
       </c>
-      <c r="K40" s="17" t="s">
-        <v>449</v>
-      </c>
       <c r="L40" s="17" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="M40" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N40" s="16"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
-        <v>108</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>62</v>
+        <v>236</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F41" s="10">
-        <v>7.5133013260082855E-3</v>
+        <v>8.654823259147992E-3</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="I41" s="6">
+        <v>10</v>
+      </c>
+      <c r="J41" s="21" t="s">
+        <v>448</v>
+      </c>
+      <c r="K41" s="17" t="s">
         <v>451</v>
       </c>
-      <c r="H41" s="10" t="s">
-        <v>451</v>
-      </c>
-      <c r="I41" s="6">
-        <v>8</v>
-      </c>
-      <c r="J41" s="21" t="s">
+      <c r="L41" s="17" t="s">
         <v>450</v>
       </c>
-      <c r="K41" s="17" t="s">
-        <v>453</v>
-      </c>
-      <c r="L41" s="17" t="s">
-        <v>452</v>
-      </c>
       <c r="M41" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N41" s="16"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
-        <v>774</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>38</v>
+        <v>243</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F42" s="7">
-        <v>1.2682547983570351E-2</v>
+        <v>1.2407844110385346E-2</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>428</v>
+        <v>388</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>428</v>
+        <v>388</v>
       </c>
       <c r="I42" s="6">
         <v>10</v>
       </c>
       <c r="J42" s="21" t="s">
+        <v>452</v>
+      </c>
+      <c r="K42" s="17" t="s">
+        <v>455</v>
+      </c>
+      <c r="L42" s="17" t="s">
         <v>454</v>
       </c>
-      <c r="K42" s="17" t="s">
-        <v>457</v>
-      </c>
-      <c r="L42" s="17" t="s">
-        <v>456</v>
-      </c>
       <c r="M42" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N42" s="16"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
-        <v>615</v>
+        <v>249</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F43" s="7">
-        <v>2.2916421048759718E-2</v>
+        <v>1.1735425361113359E-2</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>391</v>
+        <v>158</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>391</v>
+        <v>158</v>
       </c>
       <c r="I43" s="6">
         <v>10</v>
       </c>
       <c r="J43" s="22" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K43" s="17" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L43" s="17" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M43" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N43" s="16"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
-        <v>99</v>
+        <v>251</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="F44" s="7">
-        <v>2.1965990704229194E-2</v>
+        <v>9.9398063169533236E-3</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>435</v>
+        <v>106</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>435</v>
+        <v>106</v>
       </c>
       <c r="I44" s="6">
         <v>10</v>
       </c>
       <c r="J44" s="21" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K44" s="17" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="L44" s="17" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="M44" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N44" s="16"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
-        <v>617</v>
+        <v>253</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="F45" s="10">
-        <v>7.1122270218292359E-3</v>
-      </c>
-      <c r="G45" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="F45" s="7">
+        <v>2.1636851085154972E-2</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="I45" s="6">
+        <v>10</v>
+      </c>
+      <c r="J45" s="21" t="s">
+        <v>463</v>
+      </c>
+      <c r="K45" s="17" t="s">
+        <v>467</v>
+      </c>
+      <c r="L45" s="17" t="s">
         <v>466</v>
       </c>
-      <c r="H45" s="10" t="s">
-        <v>466</v>
-      </c>
-      <c r="I45" s="6">
-        <v>8</v>
-      </c>
-      <c r="J45" s="21" t="s">
-        <v>465</v>
-      </c>
-      <c r="K45" s="17" t="s">
-        <v>469</v>
-      </c>
-      <c r="L45" s="17" t="s">
-        <v>468</v>
-      </c>
       <c r="M45" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N45" s="16"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
-        <v>668</v>
+        <v>255</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="F46" s="7">
-        <v>1.3280926686582374E-2</v>
+        <v>1.3032183684948084E-2</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>477</v>
+        <v>340</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>477</v>
+        <v>490</v>
       </c>
       <c r="I46" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J46" s="21" t="s">
+        <v>468</v>
+      </c>
+      <c r="K46" s="17" t="s">
         <v>470</v>
       </c>
-      <c r="K46" s="17" t="s">
-        <v>472</v>
-      </c>
       <c r="L46" s="17" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="M46" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N46" s="16"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
-        <v>839</v>
+        <v>262</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F47" s="7">
-        <v>1.1655580919690624E-2</v>
+        <v>1.8838172247292208E-2</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>477</v>
+        <v>158</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>477</v>
+        <v>158</v>
       </c>
       <c r="I47" s="6">
         <v>10</v>
       </c>
       <c r="J47" s="21" t="s">
+        <v>471</v>
+      </c>
+      <c r="K47" s="17" t="s">
         <v>473</v>
       </c>
-      <c r="K47" s="17" t="s">
-        <v>475</v>
-      </c>
       <c r="L47" s="17" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="M47" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N47" s="16"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
-        <v>52</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>53</v>
+        <v>267</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F48" s="7">
-        <v>9.6955214810818292E-3</v>
+        <v>1.6868828351766882E-2</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>477</v>
+        <v>425</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>477</v>
+        <v>425</v>
       </c>
       <c r="I48" s="6">
         <v>10</v>
       </c>
       <c r="J48" s="21" t="s">
+        <v>474</v>
+      </c>
+      <c r="K48" s="17" t="s">
+        <v>477</v>
+      </c>
+      <c r="L48" s="17" t="s">
         <v>476</v>
       </c>
-      <c r="K48" s="17" t="s">
-        <v>479</v>
-      </c>
-      <c r="L48" s="17" t="s">
-        <v>478</v>
-      </c>
       <c r="M48" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N48" s="16"/>
     </row>
@@ -4364,7 +4440,7 @@
         <v>22</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>8</v>
@@ -4376,1339 +4452,1353 @@
         <v>2.0221683745483169E-2</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="I49" s="6">
         <v>10</v>
       </c>
       <c r="J49" s="21" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="K49" s="17" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="L49" s="16">
         <v>-100.359576893945</v>
       </c>
       <c r="M49" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N49" s="16"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
-        <v>186</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>24</v>
+        <v>270</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>80</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="F50" s="7">
-        <v>1.9348457402295335E-2</v>
+        <v>93</v>
+      </c>
+      <c r="F50" s="10">
+        <v>3.76686701981193E-3</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>392</v>
+        <v>550</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>392</v>
+        <v>442</v>
       </c>
       <c r="I50" s="6">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J50" s="21" t="s">
+        <v>481</v>
+      </c>
+      <c r="K50" s="17" t="s">
         <v>483</v>
       </c>
-      <c r="K50" s="17" t="s">
-        <v>485</v>
-      </c>
       <c r="L50" s="17" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="M50" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N50" s="16"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
-        <v>308</v>
-      </c>
-      <c r="B51" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C51" s="25" t="s">
-        <v>301</v>
-      </c>
-      <c r="D51" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="E51" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="F51" s="28">
-        <v>5.7260866255360509E-3</v>
-      </c>
-      <c r="G51" s="28"/>
-      <c r="H51" s="28"/>
-      <c r="I51" s="29">
-        <v>5</v>
-      </c>
-      <c r="J51" s="30"/>
+        <v>274</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C51" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F51" s="7">
+        <v>2.041917208193085E-2</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="I51" s="6">
+        <v>10</v>
+      </c>
+      <c r="J51" s="30" t="s">
+        <v>583</v>
+      </c>
       <c r="K51" s="31" t="s">
-        <v>211</v>
+        <v>582</v>
       </c>
       <c r="L51" s="31" t="s">
-        <v>213</v>
+        <v>581</v>
       </c>
       <c r="M51" s="16" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="N51" s="16"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
-        <v>801</v>
+        <v>277</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="F52" s="7">
-        <v>3.9252610120436918E-2</v>
-      </c>
-      <c r="G52" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="F52" s="10">
+        <v>8.2392928977464593E-3</v>
+      </c>
+      <c r="G52" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="H52" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="I52" s="6">
+        <v>4</v>
+      </c>
+      <c r="J52" s="21" t="s">
+        <v>484</v>
+      </c>
+      <c r="K52" s="17" t="s">
         <v>487</v>
       </c>
-      <c r="H52" s="7" t="s">
-        <v>487</v>
-      </c>
-      <c r="I52" s="6">
-        <v>10</v>
-      </c>
-      <c r="J52" s="21" t="s">
+      <c r="L52" s="17" t="s">
         <v>486</v>
       </c>
-      <c r="K52" s="17" t="s">
-        <v>489</v>
-      </c>
-      <c r="L52" s="17" t="s">
-        <v>488</v>
-      </c>
       <c r="M52" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N52" s="16"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F53" s="7">
-        <v>2.041917208193085E-2</v>
+        <v>1.7871180555153451E-2</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>342</v>
+        <v>564</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>492</v>
+        <v>564</v>
       </c>
       <c r="I53" s="6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J53" s="21" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="K53" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="L53" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="L53" s="17" t="s">
-        <v>214</v>
-      </c>
       <c r="M53" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N53" s="16"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
-        <v>62</v>
+        <v>305</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C54" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E54" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="F54" s="7">
-        <v>1.3994423922537694E-2</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>487</v>
-      </c>
-      <c r="H54" s="7" t="s">
-        <v>487</v>
+        <v>146</v>
+      </c>
+      <c r="C54" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F54" s="10">
+        <v>1.0355047415795852E-2</v>
+      </c>
+      <c r="G54" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="H54" s="10" t="s">
+        <v>386</v>
       </c>
       <c r="I54" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J54" s="21" t="s">
+        <v>491</v>
+      </c>
+      <c r="K54" s="17" t="s">
+        <v>492</v>
+      </c>
+      <c r="L54" s="17" t="s">
         <v>493</v>
       </c>
-      <c r="K54" s="17" t="s">
-        <v>494</v>
-      </c>
-      <c r="L54" s="17" t="s">
-        <v>495</v>
-      </c>
       <c r="M54" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N54" s="16"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
-        <v>255</v>
-      </c>
-      <c r="B55" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C55" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E55" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="F55" s="7">
-        <v>1.3032183684948084E-2</v>
+        <v>308</v>
+      </c>
+      <c r="B55" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C55" s="25" t="s">
+        <v>299</v>
+      </c>
+      <c r="D55" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="E55" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="F55" s="28">
+        <v>5.7260866255360509E-3</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>342</v>
+        <v>478</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>492</v>
-      </c>
-      <c r="I55" s="6">
-        <v>10</v>
+        <v>478</v>
+      </c>
+      <c r="I55" s="29">
+        <v>5</v>
       </c>
       <c r="J55" s="21" t="s">
+        <v>494</v>
+      </c>
+      <c r="K55" s="17" t="s">
         <v>496</v>
       </c>
-      <c r="K55" s="17" t="s">
-        <v>498</v>
-      </c>
       <c r="L55" s="17" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="M55" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N55" s="16"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
-        <v>90</v>
-      </c>
-      <c r="B56" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C56" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="F56" s="7">
-        <v>1.1808211440281434E-2</v>
-      </c>
-      <c r="G56" s="7" t="s">
-        <v>487</v>
-      </c>
-      <c r="H56" s="7" t="s">
-        <v>487</v>
+        <v>317</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C56" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E56" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="F56" s="10">
+        <v>1.2057633992142438E-2</v>
+      </c>
+      <c r="G56" s="10" t="s">
+        <v>578</v>
+      </c>
+      <c r="H56" s="10" t="s">
+        <v>578</v>
       </c>
       <c r="I56" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J56" s="21" t="s">
+        <v>497</v>
+      </c>
+      <c r="K56" s="17" t="s">
         <v>499</v>
       </c>
-      <c r="K56" s="17" t="s">
-        <v>501</v>
-      </c>
       <c r="L56" s="17" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="M56" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N56" s="16"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
-        <v>153</v>
-      </c>
-      <c r="B57" s="8" t="s">
-        <v>44</v>
+        <v>322</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="F57" s="7">
-        <v>1.1621296174072784E-2</v>
+        <v>1.2340350340891489E-2</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>429</v>
+        <v>1</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="I57" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J57" s="21" t="s">
+        <v>500</v>
+      </c>
+      <c r="K57" s="17" t="s">
         <v>502</v>
       </c>
-      <c r="K57" s="17" t="s">
-        <v>504</v>
-      </c>
       <c r="L57" s="17" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="M57" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N57" s="16"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
-        <v>199</v>
+        <v>330</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="F58" s="7">
-        <v>1.0391030746663709E-2</v>
+        <v>94</v>
+      </c>
+      <c r="F58" s="10">
+        <v>3.7043088476581844E-3</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>487</v>
+        <v>588</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>487</v>
+        <v>588</v>
       </c>
       <c r="I58" s="6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J58" s="21" t="s">
+        <v>503</v>
+      </c>
+      <c r="K58" s="17" t="s">
         <v>505</v>
       </c>
-      <c r="K58" s="17" t="s">
-        <v>507</v>
-      </c>
       <c r="L58" s="17" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="M58" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N58" s="16"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
-        <v>47</v>
-      </c>
-      <c r="B59" s="8" t="s">
-        <v>55</v>
+        <v>333</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F59" s="10">
-        <v>9.2103343959954471E-3</v>
+        <v>7.8252122337391823E-3</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>342</v>
+        <v>588</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>492</v>
+        <v>588</v>
       </c>
       <c r="I59" s="6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J59" s="21" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="K59" s="17" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="L59" s="16">
         <v>-86.822608058303601</v>
       </c>
       <c r="M59" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N59" s="16"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
-        <v>58</v>
-      </c>
-      <c r="B60" s="8" t="s">
-        <v>57</v>
+        <v>334</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F60" s="10">
-        <v>8.4847454642151248E-3</v>
+        <v>1.8709650274066469E-3</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>430</v>
+        <v>588</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>430</v>
+        <v>588</v>
       </c>
       <c r="I60" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J60" s="21" t="s">
+        <v>508</v>
+      </c>
+      <c r="K60" s="17" t="s">
         <v>510</v>
       </c>
-      <c r="K60" s="17" t="s">
-        <v>512</v>
-      </c>
       <c r="L60" s="17" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="M60" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N60" s="16"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
-        <v>651</v>
-      </c>
-      <c r="B61" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C61" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="F61" s="10">
-        <v>8.357851542356241E-3</v>
+        <v>346</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C61" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E61" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="F61" s="7">
+        <v>1.7132743239494368E-2</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>487</v>
+        <v>587</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>467</v>
+        <v>587</v>
       </c>
       <c r="I61" s="6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J61" s="21" t="s">
+        <v>511</v>
+      </c>
+      <c r="K61" s="17" t="s">
         <v>513</v>
       </c>
-      <c r="K61" s="17" t="s">
-        <v>515</v>
-      </c>
       <c r="L61" s="17" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="M61" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N61" s="16"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
-        <v>665</v>
-      </c>
-      <c r="B62" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C62" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>89</v>
+        <v>375</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C62" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E62" s="33" t="s">
+        <v>100</v>
       </c>
       <c r="F62" s="7">
-        <v>7.9611433347388412E-3</v>
+        <v>2.1210471293309406E-2</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>342</v>
+        <v>411</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>492</v>
+        <v>584</v>
       </c>
       <c r="I62" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J62" s="21" t="s">
+        <v>514</v>
+      </c>
+      <c r="K62" s="17" t="s">
         <v>516</v>
       </c>
-      <c r="K62" s="17" t="s">
-        <v>518</v>
-      </c>
       <c r="L62" s="17" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="M62" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N62" s="16"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
-        <v>723</v>
-      </c>
-      <c r="B63" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C63" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>89</v>
+        <v>376</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C63" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E63" s="33" t="s">
+        <v>100</v>
       </c>
       <c r="F63" s="10">
-        <v>6.003833613320503E-3</v>
-      </c>
-      <c r="G63" s="7" t="s">
-        <v>342</v>
+        <v>1.7115860121715138E-3</v>
+      </c>
+      <c r="G63" s="10" t="s">
+        <v>386</v>
       </c>
       <c r="H63" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="I63" s="6">
+        <v>1</v>
+      </c>
+      <c r="J63" s="21" t="s">
+        <v>517</v>
+      </c>
+      <c r="K63" s="17" t="s">
         <v>520</v>
       </c>
-      <c r="I63" s="6">
-        <v>7</v>
-      </c>
-      <c r="J63" s="21" t="s">
+      <c r="L63" s="17" t="s">
         <v>519</v>
       </c>
-      <c r="K63" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="L63" s="17" t="s">
-        <v>521</v>
-      </c>
       <c r="M63" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N63" s="16"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
-        <v>86</v>
+        <v>377</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C64" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E64" s="4" t="s">
-        <v>89</v>
+        <v>143</v>
+      </c>
+      <c r="C64" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E64" s="33" t="s">
+        <v>90</v>
       </c>
       <c r="F64" s="10">
-        <v>5.2416647144758709E-3</v>
-      </c>
-      <c r="G64" t="s">
-        <v>527</v>
+        <v>1.2373729999885532E-2</v>
+      </c>
+      <c r="G64" s="36" t="s">
+        <v>348</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>459</v>
+        <v>348</v>
       </c>
       <c r="I64" s="6">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J64" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="K64" s="17" t="s">
+        <v>524</v>
+      </c>
+      <c r="L64" s="17" t="s">
         <v>523</v>
       </c>
-      <c r="K64" s="17" t="s">
-        <v>526</v>
-      </c>
-      <c r="L64" s="17" t="s">
-        <v>525</v>
-      </c>
       <c r="M64" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N64" s="16"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
-        <v>663</v>
-      </c>
-      <c r="B65" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C65" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E65" s="4" t="s">
-        <v>89</v>
+        <v>398</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C65" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E65" s="33" t="s">
+        <v>94</v>
       </c>
       <c r="F65" s="10">
-        <v>4.6460817791641618E-3</v>
-      </c>
-      <c r="G65" s="7" t="s">
-        <v>342</v>
+        <v>8.1803746107407555E-3</v>
+      </c>
+      <c r="G65" s="10" t="s">
+        <v>577</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>520</v>
+        <v>579</v>
       </c>
       <c r="I65" s="6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J65" s="21" t="s">
+        <v>526</v>
+      </c>
+      <c r="K65" s="17" t="s">
         <v>528</v>
       </c>
-      <c r="K65" s="17" t="s">
-        <v>530</v>
-      </c>
       <c r="L65" s="17" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="M65" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N65" s="16"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
-        <v>69</v>
-      </c>
-      <c r="B66" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C66" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>89</v>
+        <v>400</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C66" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E66" s="33" t="s">
+        <v>90</v>
       </c>
       <c r="F66" s="10">
-        <v>3.7817545239335749E-3</v>
+        <v>1.6172671289420907E-2</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>455</v>
+        <v>348</v>
       </c>
       <c r="H66" s="10" t="s">
-        <v>455</v>
+        <v>348</v>
       </c>
       <c r="I66" s="6">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J66" s="21" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="K66" s="17" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="L66" s="17" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="M66" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N66" s="16"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
-        <v>251</v>
-      </c>
-      <c r="B67" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C67" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="F67" s="7">
-        <v>9.9398063169533236E-3</v>
-      </c>
-      <c r="G67" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="H67" s="7" t="s">
-        <v>106</v>
+        <v>421</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C67" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E67" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="F67" s="10">
+        <v>7.4367050813383831E-3</v>
+      </c>
+      <c r="G67" s="10" t="s">
+        <v>577</v>
+      </c>
+      <c r="H67" s="10" t="s">
+        <v>577</v>
       </c>
       <c r="I67" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J67" s="21" t="s">
+        <v>532</v>
+      </c>
+      <c r="K67" s="17" t="s">
         <v>534</v>
       </c>
-      <c r="K67" s="17" t="s">
-        <v>536</v>
-      </c>
       <c r="L67" s="17" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="M67" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N67" s="16"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
-        <v>24</v>
-      </c>
-      <c r="B68" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C68" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E68" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="F68" s="7">
-        <v>1.6640500941968742E-2</v>
-      </c>
-      <c r="G68" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H68" s="7" t="s">
-        <v>443</v>
+        <v>422</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C68" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F68" s="10">
+        <v>1.0854988342011422E-2</v>
+      </c>
+      <c r="G68" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="H68" s="10" t="s">
+        <v>475</v>
       </c>
       <c r="I68" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J68" s="21" t="s">
+        <v>535</v>
+      </c>
+      <c r="K68" s="17" t="s">
         <v>537</v>
       </c>
-      <c r="K68" s="17" t="s">
-        <v>539</v>
-      </c>
       <c r="L68" s="17" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="M68" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N68" s="16"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
-        <v>322</v>
+        <v>424</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C69" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E69" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F69" s="7">
-        <v>1.2340350340891489E-2</v>
-      </c>
-      <c r="G69" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="C69" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E69" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="F69" s="10">
+        <v>2.6571482682694911E-3</v>
+      </c>
+      <c r="G69" s="10" t="s">
+        <v>580</v>
+      </c>
+      <c r="H69" s="10" t="s">
+        <v>576</v>
+      </c>
+      <c r="I69" s="6">
         <v>1</v>
       </c>
-      <c r="H69" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="I69" s="6">
-        <v>8</v>
-      </c>
       <c r="J69" s="21" t="s">
+        <v>538</v>
+      </c>
+      <c r="K69" s="17" t="s">
         <v>540</v>
       </c>
-      <c r="K69" s="17" t="s">
-        <v>542</v>
-      </c>
       <c r="L69" s="17" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="M69" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N69" s="16"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
-        <v>812</v>
+        <v>427</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C70" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E70" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="F70" s="7">
-        <v>1.1033720708268059E-2</v>
-      </c>
-      <c r="G70" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H70" s="7" t="s">
-        <v>443</v>
+        <v>148</v>
+      </c>
+      <c r="C70" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F70" s="10">
+        <v>8.5153846040539136E-3</v>
+      </c>
+      <c r="G70" s="10" t="s">
+        <v>577</v>
+      </c>
+      <c r="H70" s="10" t="s">
+        <v>579</v>
       </c>
       <c r="I70" s="6">
         <v>10</v>
       </c>
       <c r="J70" s="21" t="s">
+        <v>541</v>
+      </c>
+      <c r="K70" s="17" t="s">
         <v>543</v>
       </c>
-      <c r="K70" s="17" t="s">
-        <v>545</v>
-      </c>
       <c r="L70" s="17" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="M70" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N70" s="16"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
-        <v>789</v>
+        <v>429</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E71" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="F71" s="7">
-        <v>2.2300002624919185E-2</v>
-      </c>
-      <c r="G71" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="H71" s="7" t="s">
-        <v>93</v>
+        <v>153</v>
+      </c>
+      <c r="C71" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F71" s="10">
+        <v>5.6402679447685958E-3</v>
+      </c>
+      <c r="G71" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="H71" s="10" t="s">
+        <v>478</v>
       </c>
       <c r="I71" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J71" s="21" t="s">
+        <v>544</v>
+      </c>
+      <c r="K71" s="17" t="s">
         <v>546</v>
       </c>
-      <c r="K71" s="17" t="s">
-        <v>548</v>
-      </c>
       <c r="L71" s="17" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="M71" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N71" s="16"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
-        <v>59</v>
-      </c>
-      <c r="B72" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C72" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F72" s="7">
-        <v>1.7395490781259557E-2</v>
-      </c>
-      <c r="G72" s="7" t="s">
-        <v>552</v>
-      </c>
-      <c r="H72" s="7" t="s">
-        <v>444</v>
+        <v>432</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C72" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E72" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="F72" s="10">
+        <v>1.2634067676041234E-2</v>
+      </c>
+      <c r="G72" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="H72" s="10" t="s">
+        <v>388</v>
       </c>
       <c r="I72" s="6">
         <v>10</v>
       </c>
       <c r="J72" s="21" t="s">
+        <v>547</v>
+      </c>
+      <c r="K72" s="17" t="s">
+        <v>548</v>
+      </c>
+      <c r="L72" s="17" t="s">
         <v>549</v>
       </c>
-      <c r="K72" s="17" t="s">
-        <v>550</v>
-      </c>
-      <c r="L72" s="17" t="s">
-        <v>551</v>
-      </c>
       <c r="M72" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N72" s="16"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
-        <v>821</v>
+        <v>435</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C73" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F73" s="7">
-        <v>9.3069760799181535E-3</v>
-      </c>
-      <c r="G73" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C73" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E73" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="F73" s="10">
+        <v>7.7415456772286593E-3</v>
+      </c>
+      <c r="G73" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="H73" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="I73" s="6">
+        <v>10</v>
+      </c>
+      <c r="J73" s="21" t="s">
+        <v>551</v>
+      </c>
+      <c r="K73" s="17" t="s">
         <v>554</v>
       </c>
-      <c r="H73" s="7" t="s">
-        <v>554</v>
-      </c>
-      <c r="I73" s="6">
-        <v>5</v>
-      </c>
-      <c r="J73" s="21" t="s">
+      <c r="L73" s="17" t="s">
         <v>553</v>
       </c>
-      <c r="K73" s="17" t="s">
-        <v>556</v>
-      </c>
-      <c r="L73" s="17" t="s">
-        <v>555</v>
-      </c>
       <c r="M73" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N73" s="16"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
-        <v>139</v>
-      </c>
-      <c r="B74" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C74" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E74" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="F74" s="10">
-        <v>6.7852963838663195E-3</v>
-      </c>
-      <c r="G74" s="7" t="s">
-        <v>554</v>
-      </c>
-      <c r="H74" s="7" t="s">
-        <v>554</v>
+        <v>443</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C74" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F74" s="7">
+        <v>1.8247361781621681E-2</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>106</v>
       </c>
       <c r="I74" s="6">
         <v>9</v>
       </c>
       <c r="J74" s="21" t="s">
+        <v>555</v>
+      </c>
+      <c r="K74" s="17" t="s">
         <v>557</v>
       </c>
-      <c r="K74" s="17" t="s">
-        <v>559</v>
-      </c>
       <c r="L74" s="17" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="M74" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N74" s="16"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
-        <v>270</v>
-      </c>
-      <c r="B75" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C75" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D75" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E75" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="F75" s="10">
-        <v>3.76686701981193E-3</v>
+        <v>445</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C75" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F75" s="7">
+        <v>1.6345485904277618E-2</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>552</v>
+        <v>390</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>444</v>
+        <v>390</v>
       </c>
       <c r="I75" s="6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J75" s="21" t="s">
+        <v>558</v>
+      </c>
+      <c r="K75" s="17" t="s">
         <v>560</v>
       </c>
-      <c r="K75" s="17" t="s">
-        <v>562</v>
-      </c>
       <c r="L75" s="17" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="M75" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N75" s="16"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
-        <v>78</v>
-      </c>
-      <c r="B76" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C76" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D76" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E76" s="9" t="s">
-        <v>91</v>
+        <v>446</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C76" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="F76" s="7">
-        <v>2.8127862242819213E-2</v>
+        <v>1.7755035386207405E-2</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>566</v>
+        <v>386</v>
       </c>
       <c r="H76" s="7" t="s">
-        <v>566</v>
+        <v>586</v>
       </c>
       <c r="I76" s="6">
         <v>10</v>
       </c>
       <c r="J76" s="21" t="s">
+        <v>561</v>
+      </c>
+      <c r="K76" s="17" t="s">
         <v>563</v>
       </c>
-      <c r="K76" s="17" t="s">
-        <v>565</v>
-      </c>
       <c r="L76" s="17" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="M76" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N76" s="16"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
-        <v>253</v>
-      </c>
-      <c r="B77" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C77" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D77" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E77" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="F77" s="7">
-        <v>2.1636851085154972E-2</v>
-      </c>
-      <c r="G77" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C77" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E77" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="F77" s="10">
+        <v>9.5218141699890037E-3</v>
+      </c>
+      <c r="G77" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="H77" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="I77" s="6">
+        <v>11</v>
+      </c>
+      <c r="J77" s="21" t="s">
+        <v>565</v>
+      </c>
+      <c r="K77" s="17" t="s">
+        <v>567</v>
+      </c>
+      <c r="L77" s="17" t="s">
         <v>566</v>
       </c>
-      <c r="H77" s="7" t="s">
-        <v>566</v>
-      </c>
-      <c r="I77" s="6">
-        <v>10</v>
-      </c>
-      <c r="J77" s="21" t="s">
-        <v>567</v>
-      </c>
-      <c r="K77" s="17" t="s">
-        <v>569</v>
-      </c>
-      <c r="L77" s="17" t="s">
-        <v>568</v>
-      </c>
       <c r="M77" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N77" s="16"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
-        <v>281</v>
+        <v>451</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C78" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E78" s="9" t="s">
-        <v>91</v>
+        <v>130</v>
+      </c>
+      <c r="C78" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>96</v>
       </c>
       <c r="F78" s="7">
-        <v>1.7871180555153451E-2</v>
+        <v>2.0763704847612412E-2</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>566</v>
+        <v>449</v>
       </c>
       <c r="H78" s="7" t="s">
-        <v>566</v>
+        <v>449</v>
       </c>
       <c r="I78" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J78" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="K78" s="17" t="s">
         <v>570</v>
       </c>
-      <c r="K78" s="17" t="s">
-        <v>572</v>
-      </c>
       <c r="L78" s="17" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="M78" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N78" s="16"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
-        <v>135</v>
-      </c>
-      <c r="B79" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C79" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E79" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="F79" s="7">
-        <v>1.1572256224504493E-2</v>
-      </c>
-      <c r="G79" s="7" t="s">
-        <v>566</v>
-      </c>
-      <c r="H79" s="7" t="s">
-        <v>566</v>
+        <v>453</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C79" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E79" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="F79" s="10">
+        <v>8.1301069626745995E-3</v>
+      </c>
+      <c r="G79" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="H79" s="10" t="s">
+        <v>478</v>
       </c>
       <c r="I79" s="6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J79" s="21" t="s">
+        <v>571</v>
+      </c>
+      <c r="K79" s="17" t="s">
         <v>573</v>
       </c>
-      <c r="K79" s="17" t="s">
-        <v>575</v>
-      </c>
       <c r="L79" s="17" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="M79" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N79" s="16"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A80" s="12">
-        <v>131</v>
+      <c r="A80" s="3">
+        <v>455</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C80" s="20" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F80" s="7">
-        <v>2.1213529829138978E-2</v>
-      </c>
-      <c r="G80" s="7"/>
-      <c r="H80" s="7"/>
+        <v>1.8203778869464636E-2</v>
+      </c>
+      <c r="G80" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="H80" s="7" t="s">
+        <v>586</v>
+      </c>
       <c r="I80" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J80" s="14" t="s">
         <v>181</v>
       </c>
       <c r="K80" s="18" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L80" s="18" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A81" s="12">
-        <v>375</v>
+      <c r="A81" s="3">
+        <v>458</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C81" s="20" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>111</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F81" s="7">
-        <v>2.1210471293309406E-2</v>
-      </c>
-      <c r="G81" s="7"/>
-      <c r="H81" s="7"/>
+        <v>1.8602455344606129E-2</v>
+      </c>
+      <c r="G81" s="7" t="s">
+        <v>585</v>
+      </c>
+      <c r="H81" s="7" t="s">
+        <v>585</v>
+      </c>
       <c r="I81" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J81" s="14" t="s">
         <v>182</v>
@@ -5717,100 +5807,112 @@
         <v>19.548992839452801</v>
       </c>
       <c r="L81" s="18" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A82" s="12">
-        <v>451</v>
+      <c r="A82" s="3">
+        <v>459</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C82" s="20" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="F82" s="7">
-        <v>2.0763704847612412E-2</v>
-      </c>
-      <c r="G82" s="7"/>
-      <c r="H82" s="7"/>
+        <v>94</v>
+      </c>
+      <c r="F82" s="10">
+        <v>1.3350039104971016E-2</v>
+      </c>
+      <c r="G82" s="10" t="s">
+        <v>577</v>
+      </c>
+      <c r="H82" s="10" t="s">
+        <v>577</v>
+      </c>
       <c r="I82" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J82" s="14" t="s">
         <v>183</v>
       </c>
       <c r="K82" s="18" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="L82" s="18" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A83" s="12">
-        <v>458</v>
+      <c r="A83" s="3">
+        <v>551</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C83" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E83" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="F83" s="7">
-        <v>1.8602455344606129E-2</v>
-      </c>
-      <c r="G83" s="7"/>
-      <c r="H83" s="7"/>
+        <v>84</v>
+      </c>
+      <c r="C83" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E83" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F83" s="10">
+        <v>2.7839409844576937E-3</v>
+      </c>
+      <c r="G83" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>377</v>
+      </c>
       <c r="I83" s="6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J83" s="14" t="s">
         <v>184</v>
       </c>
       <c r="K83" s="18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L83" s="18" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A84" s="12">
-        <v>443</v>
+      <c r="A84" s="3">
+        <v>552</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C84" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D84" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="E84" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="F84" s="7">
-        <v>1.8247361781621681E-2</v>
-      </c>
-      <c r="G84" s="7"/>
-      <c r="H84" s="7"/>
+        <v>85</v>
+      </c>
+      <c r="C84" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F84" s="10">
+        <v>2.0431194829814742E-3</v>
+      </c>
+      <c r="G84" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="H84" s="10" t="s">
+        <v>387</v>
+      </c>
       <c r="I84" s="6">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J84" s="14" t="s">
         <v>185</v>
@@ -5819,32 +5921,36 @@
         <v>22.129746078133198</v>
       </c>
       <c r="L84" s="18" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A85" s="12">
-        <v>455</v>
+      <c r="A85" s="3">
+        <v>576</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="C85" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D85" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="E85" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C85" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E85" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="F85" s="7">
-        <v>1.8203778869464636E-2</v>
-      </c>
-      <c r="G85" s="7"/>
-      <c r="H85" s="7"/>
+      <c r="F85" s="10">
+        <v>4.4154705511015406E-3</v>
+      </c>
+      <c r="G85" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="H85" s="10" t="s">
+        <v>386</v>
+      </c>
       <c r="I85" s="6">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J85" s="14" t="s">
         <v>186</v>
@@ -5853,98 +5959,110 @@
         <v>19.506940269783399</v>
       </c>
       <c r="L85" s="18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A86" s="12">
-        <v>446</v>
+      <c r="A86" s="3">
+        <v>587</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C86" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D86" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="E86" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="F86" s="7">
-        <v>1.7755035386207405E-2</v>
-      </c>
-      <c r="G86" s="7"/>
-      <c r="H86" s="7"/>
+        <v>51</v>
+      </c>
+      <c r="C86" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E86" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F86" s="10">
+        <v>9.8573962791872784E-3</v>
+      </c>
+      <c r="G86" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="H86" s="7" t="s">
+        <v>348</v>
+      </c>
       <c r="I86" s="6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J86" s="14" t="s">
         <v>187</v>
       </c>
       <c r="K86" s="18" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="L86" s="18" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A87" s="12">
-        <v>346</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="C87" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E87" s="6" t="s">
-        <v>95</v>
+      <c r="A87" s="3">
+        <v>615</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C87" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E87" s="9" t="s">
+        <v>92</v>
       </c>
       <c r="F87" s="7">
-        <v>1.7132743239494368E-2</v>
-      </c>
-      <c r="G87" s="7"/>
-      <c r="H87" s="7"/>
+        <v>2.2916421048759718E-2</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="H87" s="7" t="s">
+        <v>389</v>
+      </c>
       <c r="I87" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J87" s="14" t="s">
         <v>188</v>
       </c>
       <c r="K87" s="18" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L87" s="18" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A88" s="12">
-        <v>445</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="C88" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D88" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E88" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="F88" s="7">
-        <v>1.6345485904277618E-2</v>
-      </c>
-      <c r="G88" s="7"/>
-      <c r="H88" s="7"/>
+      <c r="A88" s="3">
+        <v>617</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C88" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E88" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F88" s="10">
+        <v>7.1122270218292359E-3</v>
+      </c>
+      <c r="G88" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="H88" s="10" t="s">
+        <v>464</v>
+      </c>
       <c r="I88" s="6">
         <v>8</v>
       </c>
@@ -5952,183 +6070,191 @@
         <v>189</v>
       </c>
       <c r="K88" s="18" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="L88" s="18" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A89" s="12">
-        <v>400</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C89" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D89" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E89" s="6" t="s">
-        <v>90</v>
+      <c r="A89" s="3">
+        <v>651</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C89" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E89" s="9" t="s">
+        <v>89</v>
       </c>
       <c r="F89" s="10">
-        <v>1.6172671289420907E-2</v>
-      </c>
-      <c r="G89" s="10"/>
-      <c r="H89" s="10"/>
+        <v>8.357851542356241E-3</v>
+      </c>
+      <c r="G89" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="H89" s="7" t="s">
+        <v>465</v>
+      </c>
       <c r="I89" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J89" s="14" t="s">
         <v>190</v>
       </c>
       <c r="K89" s="18" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="L89" s="18">
         <v>-99.179037170726104</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A90" s="12">
+      <c r="A90" s="3">
+        <v>652</v>
+      </c>
+      <c r="B90" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B90" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C90" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D90" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="E90" s="6" t="s">
-        <v>100</v>
+      <c r="C90" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E90" s="9" t="s">
+        <v>90</v>
       </c>
       <c r="F90" s="10">
-        <v>1.5680281276461372E-2</v>
-      </c>
-      <c r="G90" s="10"/>
-      <c r="H90" s="10"/>
+        <v>4.4700385807039094E-3</v>
+      </c>
+      <c r="G90" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="H90" s="10" t="s">
+        <v>377</v>
+      </c>
       <c r="I90" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J90" s="14" t="s">
         <v>191</v>
       </c>
       <c r="K90" s="18" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="L90" s="18" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A91" s="12">
-        <v>107</v>
-      </c>
-      <c r="B91" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="C91" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E91" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="F91" s="7">
-        <v>1.4652280469027492E-2</v>
+      <c r="A91" s="3">
+        <v>663</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C91" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E91" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F91" s="10">
+        <v>4.6460817791641618E-3</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>524</v>
-      </c>
-      <c r="H91" s="7" t="s">
-        <v>524</v>
+        <v>340</v>
+      </c>
+      <c r="H91" s="10" t="s">
+        <v>518</v>
       </c>
       <c r="I91" s="6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J91" s="14" t="s">
         <v>192</v>
       </c>
       <c r="K91" s="18" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="L91" s="18" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A92" s="12">
-        <v>459</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="C92" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D92" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="E92" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F92" s="10">
-        <v>1.3350039104971016E-2</v>
-      </c>
-      <c r="G92" s="10" t="s">
-        <v>579</v>
-      </c>
-      <c r="H92" s="10" t="s">
-        <v>579</v>
+      <c r="A92" s="3">
+        <v>665</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C92" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E92" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F92" s="7">
+        <v>7.9611433347388412E-3</v>
+      </c>
+      <c r="G92" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="H92" s="7" t="s">
+        <v>490</v>
       </c>
       <c r="I92" s="6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J92" s="14" t="s">
         <v>193</v>
       </c>
       <c r="K92" s="18" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L92" s="18" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A93" s="12">
-        <v>153</v>
+      <c r="A93" s="3">
+        <v>667</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C93" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E93" s="6" t="s">
-        <v>94</v>
+        <v>74</v>
+      </c>
+      <c r="C93" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E93" s="9" t="s">
+        <v>100</v>
       </c>
       <c r="F93" s="10">
-        <v>1.2999251960434605E-2</v>
+        <v>4.7611312961400119E-3</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>579</v>
+        <v>403</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>579</v>
+        <v>403</v>
       </c>
       <c r="I93" s="6">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J93" s="14" t="s">
         <v>194</v>
@@ -6137,36 +6263,36 @@
         <v>23.0440959197166</v>
       </c>
       <c r="L93" s="18" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A94" s="12">
-        <v>432</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C94" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D94" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E94" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="F94" s="10">
-        <v>1.2634067676041234E-2</v>
-      </c>
-      <c r="G94" s="10" t="s">
-        <v>390</v>
-      </c>
-      <c r="H94" s="10" t="s">
-        <v>390</v>
+      <c r="A94" s="3">
+        <v>668</v>
+      </c>
+      <c r="B94" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C94" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="F94" s="7">
+        <v>1.3280926686582374E-2</v>
+      </c>
+      <c r="G94" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="H94" s="7" t="s">
+        <v>475</v>
       </c>
       <c r="I94" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J94" s="14" t="s">
         <v>195</v>
@@ -6175,36 +6301,36 @@
         <v>19.272015139846602</v>
       </c>
       <c r="L94" s="18" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A95" s="12">
-        <v>377</v>
-      </c>
-      <c r="B95" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="C95" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D95" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="E95" s="6" t="s">
-        <v>90</v>
+      <c r="A95" s="3">
+        <v>723</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C95" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E95" s="9" t="s">
+        <v>89</v>
       </c>
       <c r="F95" s="10">
-        <v>1.2373729999885532E-2</v>
-      </c>
-      <c r="G95" s="10" t="s">
-        <v>350</v>
+        <v>6.003833613320503E-3</v>
+      </c>
+      <c r="G95" s="7" t="s">
+        <v>340</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>350</v>
+        <v>518</v>
       </c>
       <c r="I95" s="6">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J95" s="14" t="s">
         <v>196</v>
@@ -6217,32 +6343,32 @@
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A96" s="12">
-        <v>317</v>
+      <c r="A96" s="3">
+        <v>774</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C96" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D96" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E96" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="F96" s="10">
-        <v>1.2057633992142438E-2</v>
-      </c>
-      <c r="G96" s="10" t="s">
-        <v>580</v>
-      </c>
-      <c r="H96" s="10" t="s">
-        <v>580</v>
+        <v>38</v>
+      </c>
+      <c r="C96" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E96" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="F96" s="7">
+        <v>1.2682547983570351E-2</v>
+      </c>
+      <c r="G96" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="H96" s="7" t="s">
+        <v>426</v>
       </c>
       <c r="I96" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J96" s="14" t="s">
         <v>197</v>
@@ -6251,112 +6377,112 @@
         <v>20.897403003383801</v>
       </c>
       <c r="L96" s="18" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A97" s="12">
-        <v>422</v>
-      </c>
-      <c r="B97" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C97" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E97" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="F97" s="10">
-        <v>1.0854988342011422E-2</v>
-      </c>
-      <c r="G97" s="10" t="s">
-        <v>477</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>477</v>
+      <c r="A97" s="3">
+        <v>779</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C97" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E97" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="F97" s="7">
+        <v>1.4440810477971976E-2</v>
+      </c>
+      <c r="G97" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="H97" s="7" t="s">
+        <v>437</v>
       </c>
       <c r="I97" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J97" s="14" t="s">
         <v>198</v>
       </c>
       <c r="K97" s="18" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="L97" s="18" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A98" s="12">
-        <v>305</v>
+      <c r="A98" s="3">
+        <v>789</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C98" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D98" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="E98" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="F98" s="10">
-        <v>1.0355047415795852E-2</v>
-      </c>
-      <c r="G98" s="10" t="s">
-        <v>388</v>
-      </c>
-      <c r="H98" s="10" t="s">
-        <v>388</v>
+        <v>16</v>
+      </c>
+      <c r="C98" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E98" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F98" s="7">
+        <v>2.2300002624919185E-2</v>
+      </c>
+      <c r="G98" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="H98" s="7" t="s">
+        <v>93</v>
       </c>
       <c r="I98" s="6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J98" s="14" t="s">
         <v>199</v>
       </c>
       <c r="K98" s="18" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="L98" s="18" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A99" s="12">
-        <v>449</v>
+      <c r="A99" s="3">
+        <v>801</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C99" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D99" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="E99" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="F99" s="10">
-        <v>9.5218141699890037E-3</v>
-      </c>
-      <c r="G99" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>350</v>
+        <v>5</v>
+      </c>
+      <c r="C99" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E99" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F99" s="7">
+        <v>3.9252610120436918E-2</v>
+      </c>
+      <c r="G99" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="H99" s="7" t="s">
+        <v>485</v>
       </c>
       <c r="I99" s="6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J99" s="14" t="s">
         <v>200</v>
@@ -6365,33 +6491,33 @@
         <v>19.3884836634716</v>
       </c>
       <c r="L99" s="18" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A100" s="12">
-        <v>427</v>
+      <c r="A100" s="3">
+        <v>802</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C100" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D100" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="E100" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C100" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E100" s="9" t="s">
         <v>94</v>
       </c>
       <c r="F100" s="10">
-        <v>8.5153846040539136E-3</v>
+        <v>5.0952928104922666E-3</v>
       </c>
       <c r="G100" s="10" t="s">
+        <v>577</v>
+      </c>
+      <c r="H100" s="10" t="s">
         <v>579</v>
-      </c>
-      <c r="H100" s="10" t="s">
-        <v>581</v>
       </c>
       <c r="I100" s="6">
         <v>10</v>
@@ -6400,74 +6526,74 @@
         <v>201</v>
       </c>
       <c r="K100" s="18" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="L100" s="18" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A101" s="12">
-        <v>398</v>
+      <c r="A101" s="3">
+        <v>807</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="C101" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D101" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E101" s="6" t="s">
-        <v>94</v>
+        <v>87</v>
+      </c>
+      <c r="C101" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E101" s="9" t="s">
+        <v>90</v>
       </c>
       <c r="F101" s="10">
-        <v>8.1803746107407555E-3</v>
-      </c>
-      <c r="G101" s="10" t="s">
-        <v>579</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>581</v>
+        <v>1.7718440648280807E-3</v>
+      </c>
+      <c r="G101" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="H101" s="7" t="s">
+        <v>348</v>
       </c>
       <c r="I101" s="6">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J101" s="14" t="s">
         <v>202</v>
       </c>
       <c r="K101" s="18" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="L101" s="18" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A102" s="12">
-        <v>453</v>
+      <c r="A102" s="3">
+        <v>808</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="C102" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D102" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E102" s="6" t="s">
-        <v>95</v>
+        <v>82</v>
+      </c>
+      <c r="C102" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D102" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E102" s="9" t="s">
+        <v>100</v>
       </c>
       <c r="F102" s="10">
-        <v>8.1301069626745995E-3</v>
+        <v>2.8538681137612394E-3</v>
       </c>
       <c r="G102" s="10" t="s">
-        <v>480</v>
+        <v>386</v>
       </c>
       <c r="H102" s="10" t="s">
-        <v>480</v>
+        <v>386</v>
       </c>
       <c r="I102" s="6">
         <v>5</v>
@@ -6479,33 +6605,33 @@
         <v>20.6076550152689</v>
       </c>
       <c r="L102" s="18" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A103" s="12">
-        <v>435</v>
+      <c r="A103" s="3">
+        <v>812</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="C103" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D103" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="E103" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="F103" s="10">
-        <v>7.7415456772286593E-3</v>
-      </c>
-      <c r="G103" s="10" t="s">
-        <v>388</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>388</v>
+        <v>48</v>
+      </c>
+      <c r="C103" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E103" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="F103" s="7">
+        <v>1.1033720708268059E-2</v>
+      </c>
+      <c r="G103" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H103" s="7" t="s">
+        <v>441</v>
       </c>
       <c r="I103" s="6">
         <v>10</v>
@@ -6517,74 +6643,74 @@
         <v>19.417376983685099</v>
       </c>
       <c r="L103" s="18" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A104" s="12">
-        <v>421</v>
-      </c>
-      <c r="B104" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C104" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D104" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="E104" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F104" s="10">
-        <v>7.4367050813383831E-3</v>
-      </c>
-      <c r="G104" s="10" t="s">
-        <v>579</v>
-      </c>
-      <c r="H104" s="10" t="s">
-        <v>579</v>
+      <c r="A104" s="3">
+        <v>814</v>
+      </c>
+      <c r="B104" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C104" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E104" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F104" s="7">
+        <v>1.1317007292279867E-2</v>
+      </c>
+      <c r="G104" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="H104" s="7" t="s">
+        <v>340</v>
       </c>
       <c r="I104" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J104" s="14" t="s">
         <v>205</v>
       </c>
       <c r="K104" s="18" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="L104" s="18" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A105" s="12">
-        <v>429</v>
+      <c r="A105" s="3">
+        <v>819</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="C105" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D105" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E105" s="6" t="s">
-        <v>95</v>
+        <v>65</v>
+      </c>
+      <c r="C105" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D105" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E105" s="9" t="s">
+        <v>90</v>
       </c>
       <c r="F105" s="10">
-        <v>5.6402679447685958E-3</v>
+        <v>6.4709636133180506E-3</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>480</v>
+        <v>366</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>480</v>
+        <v>366</v>
       </c>
       <c r="I105" s="6">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J105" s="14" t="s">
         <v>206</v>
@@ -6593,36 +6719,36 @@
         <v>20.643285180687901</v>
       </c>
       <c r="L105" s="18" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A106" s="12">
-        <v>137</v>
+      <c r="A106" s="3">
+        <v>821</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C106" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D106" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="E106" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="F106" s="10">
-        <v>4.9108683201326657E-3</v>
-      </c>
-      <c r="G106" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="H106" s="10" t="s">
-        <v>348</v>
+        <v>54</v>
+      </c>
+      <c r="C106" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E106" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F106" s="7">
+        <v>9.3069760799181535E-3</v>
+      </c>
+      <c r="G106" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="H106" s="7" t="s">
+        <v>552</v>
       </c>
       <c r="I106" s="6">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J106" s="14" t="s">
         <v>207</v>
@@ -6631,74 +6757,74 @@
         <v>19.3827979499045</v>
       </c>
       <c r="L106" s="18" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A107" s="12">
-        <v>14</v>
+      <c r="A107" s="3">
+        <v>839</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C107" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D107" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E107" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="F107" s="10">
-        <v>3.8276328024454062E-3</v>
-      </c>
-      <c r="G107" s="10" t="s">
-        <v>388</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>388</v>
+        <v>43</v>
+      </c>
+      <c r="C107" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E107" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="F107" s="7">
+        <v>1.1655580919690624E-2</v>
+      </c>
+      <c r="G107" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="H107" s="7" t="s">
+        <v>475</v>
       </c>
       <c r="I107" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J107" s="14" t="s">
         <v>208</v>
       </c>
       <c r="K107" s="18" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="L107" s="18" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A108" s="12">
-        <v>424</v>
+      <c r="A108" s="3">
+        <v>858</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="C108" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D108" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="E108" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C108" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E108" s="9" t="s">
         <v>100</v>
       </c>
       <c r="F108" s="10">
-        <v>2.6571482682694911E-3</v>
+        <v>5.1049684701715108E-3</v>
       </c>
       <c r="G108" s="10" t="s">
-        <v>582</v>
+        <v>411</v>
       </c>
       <c r="H108" s="10" t="s">
-        <v>578</v>
+        <v>411</v>
       </c>
       <c r="I108" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J108" s="14" t="s">
         <v>209</v>
@@ -6707,60 +6833,60 @@
         <v>19.165077004486399</v>
       </c>
       <c r="L108" s="18" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A109" s="12">
-        <v>376</v>
+      <c r="A109" s="3">
+        <v>890</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="C109" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="D109" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="E109" s="6" t="s">
-        <v>100</v>
+        <v>68</v>
+      </c>
+      <c r="C109" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D109" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E109" s="9" t="s">
+        <v>90</v>
       </c>
       <c r="F109" s="10">
-        <v>1.7115860121715138E-3</v>
+        <v>5.9978222327954078E-3</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>388</v>
+        <v>366</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>388</v>
+        <v>366</v>
       </c>
       <c r="I109" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J109" s="14" t="s">
         <v>210</v>
       </c>
       <c r="K109" s="18" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="L109" s="18" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="1048576" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M1048576" s="16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I79" xr:uid="{3A16AC06-11F1-411E-BC54-C20D4B63FCD4}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I79">
-      <sortCondition ref="E1:E79"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I109">
+      <sortCondition ref="A1:A79"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="F80:H109">
-    <cfRule type="colorScale" priority="9">
+  <conditionalFormatting sqref="F14:H15 F17 F18:H18 F20:H21 F23:H33 F64 H64 F65:H79 F35:H63 F2 F3:H12">
+    <cfRule type="colorScale" priority="57">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6771,8 +6897,30 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F80:H109">
+  <conditionalFormatting sqref="F64 H64 F65:H79 F2 F3:H63">
+    <cfRule type="colorScale" priority="67">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F80:H83 F84 F85:H109">
     <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6795,6 +6943,30 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="G26">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G34:G35">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="H19">
     <cfRule type="colorScale" priority="6">
       <colorScale>
@@ -6807,32 +6979,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G26">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H26">
     <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G34:G35">
-    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6857,30 +7005,6 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="H35">
     <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:H12 F14:H15 F17 F18:H18 F20:H21 F23:H33 F35:H63 F64 H64 F65:H79">
-    <cfRule type="colorScale" priority="57">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:H63 F64 H64 F65:H79">
-    <cfRule type="colorScale" priority="67">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6933,9 +7057,18 @@
     <hyperlink ref="J19" r:id="rId39" xr:uid="{E8908A6E-9D09-45CD-B809-26E40ED23C7B}"/>
     <hyperlink ref="J20" r:id="rId40" xr:uid="{CFA7C5A1-E280-4098-8DEA-A826A1DBBD8D}"/>
     <hyperlink ref="J43" r:id="rId41" xr:uid="{3F69C7F5-A773-4647-B0DF-39142BA30056}"/>
+    <hyperlink ref="J2" r:id="rId42" xr:uid="{A03EFF8D-330E-4B18-8F1F-027B5C632B69}"/>
+    <hyperlink ref="J3" r:id="rId43" xr:uid="{23129F5F-255C-42BB-AEA2-961A34D35337}"/>
+    <hyperlink ref="J4" r:id="rId44" xr:uid="{98DE9459-EF93-42B0-AF3D-CE841DBD9BDA}"/>
+    <hyperlink ref="J5" r:id="rId45" xr:uid="{3452D68E-1E29-41F4-8AD6-AD3E94CB3AF5}"/>
+    <hyperlink ref="J6" r:id="rId46" xr:uid="{9C89471F-7C10-4329-9EF4-388DA7509499}"/>
+    <hyperlink ref="J7" r:id="rId47" xr:uid="{494F09D5-D3C8-494F-9FA3-2C25B4C973C4}"/>
+    <hyperlink ref="J8" r:id="rId48" xr:uid="{358B159E-F3A5-4BA8-B7A2-6B1357047E18}"/>
+    <hyperlink ref="J9" r:id="rId49" xr:uid="{262C94FA-5979-488D-9E95-0BD78A63A507}"/>
+    <hyperlink ref="J10" r:id="rId50" xr:uid="{7B856CC2-7A3B-45A9-9C88-B26B1D45515A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId42"/>
+  <pageSetup orientation="portrait" r:id="rId51"/>
 </worksheet>
 </file>
 
@@ -6978,10 +7111,10 @@
         <v>162</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -7007,10 +7140,10 @@
         <v>163</v>
       </c>
       <c r="H3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -7036,10 +7169,10 @@
         <v>164</v>
       </c>
       <c r="H4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -7065,10 +7198,10 @@
         <v>165</v>
       </c>
       <c r="H5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -7094,10 +7227,10 @@
         <v>166</v>
       </c>
       <c r="H6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -7123,10 +7256,10 @@
         <v>167</v>
       </c>
       <c r="H7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -7152,10 +7285,10 @@
         <v>168</v>
       </c>
       <c r="H8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I8" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -7181,10 +7314,10 @@
         <v>169</v>
       </c>
       <c r="H9" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I9" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -7210,10 +7343,10 @@
         <v>170</v>
       </c>
       <c r="H10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I10" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -7239,10 +7372,10 @@
         <v>171</v>
       </c>
       <c r="H11" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I11" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -7268,10 +7401,10 @@
         <v>172</v>
       </c>
       <c r="H12" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="I12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -7297,10 +7430,10 @@
         <v>173</v>
       </c>
       <c r="H13" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I13" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -7326,10 +7459,10 @@
         <v>174</v>
       </c>
       <c r="H14" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I14" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -7355,10 +7488,10 @@
         <v>175</v>
       </c>
       <c r="H15" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I15" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -7384,10 +7517,10 @@
         <v>176</v>
       </c>
       <c r="H16" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="I16" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -7413,10 +7546,10 @@
         <v>177</v>
       </c>
       <c r="H17" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I17" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -7442,10 +7575,10 @@
         <v>178</v>
       </c>
       <c r="H18" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="I18" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -7471,10 +7604,10 @@
         <v>179</v>
       </c>
       <c r="H19" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I19" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -7500,10 +7633,10 @@
         <v>180</v>
       </c>
       <c r="H20" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="I20" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -7529,10 +7662,10 @@
         <v>181</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I21" s="18" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -7561,7 +7694,7 @@
         <v>19.548992839452801</v>
       </c>
       <c r="I22" s="18" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -7587,10 +7720,10 @@
         <v>183</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I23" s="18" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -7616,10 +7749,10 @@
         <v>184</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="I24" s="18" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -7648,7 +7781,7 @@
         <v>22.129746078133198</v>
       </c>
       <c r="I25" s="18" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -7677,7 +7810,7 @@
         <v>19.506940269783399</v>
       </c>
       <c r="I26" s="18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -7703,10 +7836,10 @@
         <v>187</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="I27" s="18" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -7732,10 +7865,10 @@
         <v>188</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="I28" s="18" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -7761,10 +7894,10 @@
         <v>189</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="I29" s="18" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -7790,7 +7923,7 @@
         <v>190</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="I30" s="18">
         <v>-99.179037170726104</v>
@@ -7819,10 +7952,10 @@
         <v>191</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I31" s="18" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -7848,10 +7981,10 @@
         <v>192</v>
       </c>
       <c r="H32" s="18" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I32" s="18" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -7877,10 +8010,10 @@
         <v>193</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="I33" s="18" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -7909,7 +8042,7 @@
         <v>23.0440959197166</v>
       </c>
       <c r="I34" s="18" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -7938,7 +8071,7 @@
         <v>19.272015139846602</v>
       </c>
       <c r="I35" s="18" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -7996,7 +8129,7 @@
         <v>20.897403003383801</v>
       </c>
       <c r="I37" s="18" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -8022,10 +8155,10 @@
         <v>198</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="I38" s="18" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -8051,10 +8184,10 @@
         <v>199</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="I39" s="18" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -8083,7 +8216,7 @@
         <v>19.3884836634716</v>
       </c>
       <c r="I40" s="18" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -8109,10 +8242,10 @@
         <v>201</v>
       </c>
       <c r="H41" s="18" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I41" s="18" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -8138,10 +8271,10 @@
         <v>202</v>
       </c>
       <c r="H42" s="18" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="I42" s="18" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -8170,7 +8303,7 @@
         <v>20.6076550152689</v>
       </c>
       <c r="I43" s="18" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -8199,7 +8332,7 @@
         <v>19.417376983685099</v>
       </c>
       <c r="I44" s="18" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -8225,10 +8358,10 @@
         <v>205</v>
       </c>
       <c r="H45" s="18" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I45" s="18" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -8257,7 +8390,7 @@
         <v>20.643285180687901</v>
       </c>
       <c r="I46" s="18" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -8286,7 +8419,7 @@
         <v>19.3827979499045</v>
       </c>
       <c r="I47" s="18" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -8312,10 +8445,10 @@
         <v>208</v>
       </c>
       <c r="H48" s="18" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I48" s="18" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -8344,7 +8477,7 @@
         <v>19.165077004486399</v>
       </c>
       <c r="I49" s="18" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -8370,16 +8503,16 @@
         <v>210</v>
       </c>
       <c r="H50" s="18" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="I50" s="18" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:F50" xr:uid="{52CE2E43-0DFC-40AA-B05B-C9CB075EA9CC}"/>
-  <conditionalFormatting sqref="E3:E50">
-    <cfRule type="colorScale" priority="56">
+  <conditionalFormatting sqref="E3 E5 E7:E10 E12:E15 E17:E50">
+    <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -8390,8 +8523,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5 E3 E7:E10 E12:E15 E17:E50">
-    <cfRule type="colorScale" priority="50">
+  <conditionalFormatting sqref="E3:E50">
+    <cfRule type="colorScale" priority="56">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
